--- a/output/tables/mesh/experiment_2/stats-level_glm_level1.xlsx
+++ b/output/tables/mesh/experiment_2/stats-level_glm_level1.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,6 +385,11 @@
           <t>mesh_term</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>stats.sign</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -393,20 +398,25 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.004123741281820789</v>
+        <v>-0.008475714782482401</v>
       </c>
       <c r="C2">
-        <v>0.01171245002045036</v>
+        <v>0.00513320456866282</v>
       </c>
       <c r="D2">
-        <v>0.3520818679798494</v>
+        <v>-1.651154686923045</v>
       </c>
       <c r="E2">
-        <v>0.7247768661375179</v>
+        <v>0.09870699301225966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Eukaryota</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -417,20 +427,25 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.01073059245635813</v>
+        <v>-0.005755412148764353</v>
       </c>
       <c r="C3">
-        <v>0.01159398489439228</v>
+        <v>0.008485518683350741</v>
       </c>
       <c r="D3">
-        <v>0.92553100198951</v>
+        <v>-0.6782628574086964</v>
       </c>
       <c r="E3">
-        <v>0.3546897651527066</v>
+        <v>0.4976050443098779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Investigative Techniques</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -441,20 +456,25 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.007624668651695395</v>
+        <v>-0.003608591230488276</v>
       </c>
       <c r="C4">
-        <v>0.01343203348155087</v>
+        <v>0.008254034019105076</v>
       </c>
       <c r="D4">
-        <v>0.5676481273046265</v>
+        <v>-0.4371912233625043</v>
       </c>
       <c r="E4">
-        <v>0.5702739207297273</v>
+        <v>0.6619726742207138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Environment and Public Health</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -465,20 +485,25 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.01191806275939768</v>
+        <v>0.003216532824229183</v>
       </c>
       <c r="C5">
-        <v>0.01488104194446039</v>
+        <v>0.007989481986750147</v>
       </c>
       <c r="D5">
-        <v>0.8008889971467545</v>
+        <v>0.402595916676891</v>
       </c>
       <c r="E5">
-        <v>0.4231959104217797</v>
+        <v>0.6872455140610555</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Information Science</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -489,20 +514,25 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.003252708562625903</v>
+        <v>-0.00832094252732707</v>
       </c>
       <c r="C6">
-        <v>0.01286397837009484</v>
+        <v>0.008343613309927807</v>
       </c>
       <c r="D6">
-        <v>0.2528540136687063</v>
+        <v>-0.997282857946717</v>
       </c>
       <c r="E6">
-        <v>0.8003810266514355</v>
+        <v>0.3186272319594334</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Health Care Quality, Access, and Evaluation</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -513,20 +543,25 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.02247756224779169</v>
+        <v>0.01325485087409543</v>
       </c>
       <c r="C7">
-        <v>0.01436130639217183</v>
+        <v>0.006653767638158191</v>
       </c>
       <c r="D7">
-        <v>1.565147461796647</v>
+        <v>1.992082019528482</v>
       </c>
       <c r="E7">
-        <v>0.1175483371100745</v>
+        <v>0.04636205943448692</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Diagnosis</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -537,20 +572,25 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.01562432421494659</v>
+        <v>0.0004464322779452414</v>
       </c>
       <c r="C8">
-        <v>0.01548986811254355</v>
+        <v>0.00659727202452429</v>
       </c>
       <c r="D8">
-        <v>1.008680261279575</v>
+        <v>0.06766922392857255</v>
       </c>
       <c r="E8">
-        <v>0.3131280011653594</v>
+        <v>0.9460489488821552</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Persons</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -561,20 +601,25 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.02363319396905329</v>
+        <v>0.0131956419735254</v>
       </c>
       <c r="C9">
-        <v>0.0178696601642707</v>
+        <v>0.007794645234987047</v>
       </c>
       <c r="D9">
-        <v>1.322531808204525</v>
+        <v>1.692911168592438</v>
       </c>
       <c r="E9">
-        <v>0.1859911246710405</v>
+        <v>0.09047237711414877</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -585,20 +630,25 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.03651974466261174</v>
+        <v>0.02193670413617474</v>
       </c>
       <c r="C10">
-        <v>0.0213509041924521</v>
+        <v>0.009991148191344567</v>
       </c>
       <c r="D10">
-        <v>1.7104542427539</v>
+        <v>2.195613929055594</v>
       </c>
       <c r="E10">
-        <v>0.08718190788260462</v>
+        <v>0.02811958840738123</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Mathematical Concepts</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -609,20 +659,25 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.004583367999737158</v>
+        <v>0.001880757629575273</v>
       </c>
       <c r="C11">
-        <v>0.01916512968752853</v>
+        <v>0.008551963756664069</v>
       </c>
       <c r="D11">
-        <v>0.2391514210686363</v>
+        <v>0.2199211412828666</v>
       </c>
       <c r="E11">
-        <v>0.8109881701042466</v>
+        <v>0.8259325709979959</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -633,20 +688,25 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.03120504480597159</v>
+        <v>-0.02999636738569342</v>
       </c>
       <c r="C12">
-        <v>0.02312651469386715</v>
+        <v>0.0107144620357381</v>
       </c>
       <c r="D12">
-        <v>-1.349318962197394</v>
+        <v>-2.799614883662894</v>
       </c>
       <c r="E12">
-        <v>0.177234537529861</v>
+        <v>0.005116360688462788</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Behavior and Behavior Mechanisms</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>**</t>
         </is>
       </c>
     </row>
@@ -657,20 +717,25 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.03418326250020366</v>
+        <v>-0.02742558946750381</v>
       </c>
       <c r="C13">
-        <v>0.02340314686933305</v>
+        <v>0.01059666237667933</v>
       </c>
       <c r="D13">
-        <v>-1.460626756352866</v>
+        <v>-2.58813468737674</v>
       </c>
       <c r="E13">
-        <v>0.1441178993525119</v>
+        <v>0.00964972413076428</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Psychological Phenomena</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>**</t>
         </is>
       </c>
     </row>
@@ -681,20 +746,25 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.01194975634774235</v>
+        <v>-0.01291616183164804</v>
       </c>
       <c r="C14">
-        <v>0.02078953105729803</v>
+        <v>0.01164029566412912</v>
       </c>
       <c r="D14">
-        <v>0.5747968203230568</v>
+        <v>-1.1096077113789</v>
       </c>
       <c r="E14">
-        <v>0.5654287174508092</v>
+        <v>0.2671681068610686</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Natural Science Disciplines</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -705,20 +775,25 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.01769951259126079</v>
+        <v>-0.0171790576601876</v>
       </c>
       <c r="C15">
-        <v>0.02158571465818489</v>
+        <v>0.008907699607862786</v>
       </c>
       <c r="D15">
-        <v>-0.8199641694304282</v>
+        <v>-1.928562750928839</v>
       </c>
       <c r="E15">
-        <v>0.4122365335018406</v>
+        <v>0.05378516704089294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Health Services Administration</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -729,20 +804,25 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.009795923921687431</v>
+        <v>-0.0156350052890929</v>
       </c>
       <c r="C16">
-        <v>0.02224732315120452</v>
+        <v>0.009043192300733081</v>
       </c>
       <c r="D16">
-        <v>-0.4403192175125598</v>
+        <v>-1.728925446805489</v>
       </c>
       <c r="E16">
-        <v>0.6597059239682541</v>
+        <v>0.08382243906084788</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Geographic Locations</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -753,20 +833,25 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.007371212942647956</v>
+        <v>-0.01101502421913512</v>
       </c>
       <c r="C17">
-        <v>0.02493979223860967</v>
+        <v>0.009992456481968469</v>
       </c>
       <c r="D17">
-        <v>0.295560318711736</v>
+        <v>-1.102333969531105</v>
       </c>
       <c r="E17">
-        <v>0.7675658814175612</v>
+        <v>0.2703165064149065</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Health Care Facilities, Manpower, and Services</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -777,20 +862,25 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.01989376065099961</v>
+        <v>-0.01322506611329016</v>
       </c>
       <c r="C18">
-        <v>0.02433580196398598</v>
+        <v>0.01137435114140975</v>
       </c>
       <c r="D18">
-        <v>-0.8174688748881156</v>
+        <v>-1.162709498666931</v>
       </c>
       <c r="E18">
-        <v>0.4136605294466743</v>
+        <v>0.2449473864388725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Physiological Phenomena</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -801,20 +891,25 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.01787263686569638</v>
+        <v>0.001974438859813122</v>
       </c>
       <c r="C19">
-        <v>0.02462965494060864</v>
+        <v>0.01183145973347626</v>
       </c>
       <c r="D19">
-        <v>0.7256551871633615</v>
+        <v>0.166880410726209</v>
       </c>
       <c r="E19">
-        <v>0.4680501801699647</v>
+        <v>0.8674641469710436</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>Physical Phenomena</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -825,20 +920,25 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.0502893212275629</v>
+        <v>-0.02400490242813999</v>
       </c>
       <c r="C20">
-        <v>0.02686365969364507</v>
+        <v>0.01122694067493862</v>
       </c>
       <c r="D20">
-        <v>-1.872020484217921</v>
+        <v>-2.138151712311531</v>
       </c>
       <c r="E20">
-        <v>0.0612037696163709</v>
+        <v>0.0325044320211571</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>Social Sciences</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -849,20 +949,25 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.007950868810761291</v>
+        <v>-0.01187383452271966</v>
       </c>
       <c r="C21">
-        <v>0.02073736540534542</v>
+        <v>0.008581307238178454</v>
       </c>
       <c r="D21">
-        <v>0.3834078560776006</v>
+        <v>-1.383685980836657</v>
       </c>
       <c r="E21">
-        <v>0.7014173792774256</v>
+        <v>0.1664546280563421</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>Pathological Conditions, Signs and Symptoms</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -873,20 +978,25 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.02612276664797638</v>
+        <v>-0.006472588092971089</v>
       </c>
       <c r="C22">
-        <v>0.02355675285431198</v>
+        <v>0.01014089477437207</v>
       </c>
       <c r="D22">
-        <v>1.108929011121951</v>
+        <v>-0.6382659752400277</v>
       </c>
       <c r="E22">
-        <v>0.2674608074147826</v>
+        <v>0.5233005566236071</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>Therapeutics</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -897,20 +1007,25 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.06103545304568189</v>
+        <v>-0.01351820637137212</v>
       </c>
       <c r="C23">
-        <v>0.02905840750903886</v>
+        <v>0.01378867062994513</v>
       </c>
       <c r="D23">
-        <v>2.100440398418128</v>
+        <v>-0.9803850374099414</v>
       </c>
       <c r="E23">
-        <v>0.03569011842354605</v>
+        <v>0.3268960927402136</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>Genetic Phenomena</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -921,20 +1036,25 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.001043605482404629</v>
+        <v>-0.01861712042437113</v>
       </c>
       <c r="C24">
-        <v>0.02933160792997002</v>
+        <v>0.01348122884459471</v>
       </c>
       <c r="D24">
-        <v>-0.03557955243695687</v>
+        <v>-1.380966129941162</v>
       </c>
       <c r="E24">
-        <v>0.9716176127887691</v>
+        <v>0.1672893749907523</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>Musculoskeletal and Neural Physiological Phenomena</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -945,20 +1065,25 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.008420966898782429</v>
+        <v>0.01838248377624672</v>
       </c>
       <c r="C25">
-        <v>0.02495293420360454</v>
+        <v>0.01045410418002407</v>
       </c>
       <c r="D25">
-        <v>0.3374740152829798</v>
+        <v>1.758398755138902</v>
       </c>
       <c r="E25">
-        <v>0.735759597231054</v>
+        <v>0.07867968480708418</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>Technology, Industry, and Agriculture</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -969,20 +1094,25 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.01859859971412807</v>
+        <v>0.01151155404756585</v>
       </c>
       <c r="C26">
-        <v>0.03448307159264383</v>
+        <v>0.01460811258822534</v>
       </c>
       <c r="D26">
-        <v>0.5393544964276226</v>
+        <v>0.7880247347521525</v>
       </c>
       <c r="E26">
-        <v>0.5896422724985635</v>
+        <v>0.4306822379300197</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Biological Phenomena</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -993,20 +1123,25 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.04639634401583818</v>
+        <v>0.0346930487612666</v>
       </c>
       <c r="C27">
-        <v>0.02577552480668989</v>
+        <v>0.009019008701857711</v>
       </c>
       <c r="D27">
-        <v>1.80001549391523</v>
+        <v>3.846658752432584</v>
       </c>
       <c r="E27">
-        <v>0.0718581917658463</v>
+        <v>0.0001197395574908256</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>Neoplasms</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>***</t>
         </is>
       </c>
     </row>
@@ -1017,20 +1152,25 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.001262138201637078</v>
+        <v>0.008449242188402765</v>
       </c>
       <c r="C28">
-        <v>0.03623280753559788</v>
+        <v>0.01490636052079018</v>
       </c>
       <c r="D28">
-        <v>0.03483412651357632</v>
+        <v>0.5668212691232342</v>
       </c>
       <c r="E28">
-        <v>0.9722120081134195</v>
+        <v>0.5708356186636665</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>Chemical Phenomena</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1041,20 +1181,25 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.05716610025889696</v>
+        <v>0.02039879569662755</v>
       </c>
       <c r="C29">
-        <v>0.03315400386745411</v>
+        <v>0.01373953076225763</v>
       </c>
       <c r="D29">
-        <v>1.724259322869131</v>
+        <v>1.484679211364544</v>
       </c>
       <c r="E29">
-        <v>0.0846610390541446</v>
+        <v>0.1376288211758379</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>Amino Acids, Peptides, and Proteins</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1065,20 +1210,25 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.09991147588787019</v>
+        <v>-0.06082222147980457</v>
       </c>
       <c r="C30">
-        <v>0.03061022819283887</v>
+        <v>0.0128979877759042</v>
       </c>
       <c r="D30">
-        <v>-3.263989907505624</v>
+        <v>-4.715636464893509</v>
       </c>
       <c r="E30">
-        <v>0.001098550785812458</v>
+        <v>2.409563281887003E-06</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>Health Occupations</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>****</t>
         </is>
       </c>
     </row>
@@ -1089,20 +1239,25 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.02331547717895013</v>
+        <v>-0.01851097438474544</v>
       </c>
       <c r="C31">
-        <v>0.02720952872682036</v>
+        <v>0.01130707763010864</v>
       </c>
       <c r="D31">
-        <v>0.8568864758016969</v>
+        <v>-1.637113937862615</v>
       </c>
       <c r="E31">
-        <v>0.3915076277343874</v>
+        <v>0.1016066648406727</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>Nervous System Diseases</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1113,20 +1268,25 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.02347220054832351</v>
+        <v>-0.01489620030501303</v>
       </c>
       <c r="C32">
-        <v>0.02671671223727239</v>
+        <v>0.01153278003111527</v>
       </c>
       <c r="D32">
-        <v>0.878558721592155</v>
+        <v>-1.291640026500402</v>
       </c>
       <c r="E32">
-        <v>0.3796405854221782</v>
+        <v>0.1964818357055724</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>Chemical Actions and Uses</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1137,20 +1297,25 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.0019907462590275</v>
+        <v>-0.007563095479748976</v>
       </c>
       <c r="C33">
-        <v>0.03735900910170136</v>
+        <v>0.0152994743733819</v>
       </c>
       <c r="D33">
-        <v>-0.05328691276602516</v>
+        <v>-0.4943369487848082</v>
       </c>
       <c r="E33">
-        <v>0.9575033074870367</v>
+        <v>0.6210682347723342</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>Nervous System</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1161,20 +1326,25 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.00167697979750836</v>
+        <v>-0.02768945814607639</v>
       </c>
       <c r="C34">
-        <v>0.03148242146733282</v>
+        <v>0.01367310212005838</v>
       </c>
       <c r="D34">
-        <v>0.05326717956712601</v>
+        <v>-2.025104318167571</v>
       </c>
       <c r="E34">
-        <v>0.9575190299722376</v>
+        <v>0.04285665360525117</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>Population Characteristics</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -1185,20 +1355,25 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.03099039773166076</v>
+        <v>0.0164078227780237</v>
       </c>
       <c r="C35">
-        <v>0.02829384393326567</v>
+        <v>0.0114307964356061</v>
       </c>
       <c r="D35">
-        <v>1.09530531817293</v>
+        <v>1.435405036775436</v>
       </c>
       <c r="E35">
-        <v>0.2733828983834354</v>
+        <v>0.1511717115565464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>Equipment and Supplies</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1209,20 +1384,25 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.03121252569291772</v>
+        <v>-0.03415763181440723</v>
       </c>
       <c r="C36">
-        <v>0.0379701546820526</v>
+        <v>0.01525981995147892</v>
       </c>
       <c r="D36">
-        <v>-0.8220278783238928</v>
+        <v>-2.238403331298598</v>
       </c>
       <c r="E36">
-        <v>0.4110610304895165</v>
+        <v>0.02519476499514773</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>Health Care Economics and Organizations</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -1233,20 +1413,25 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.03623631528930488</v>
+        <v>0.003683375782054717</v>
       </c>
       <c r="C37">
-        <v>0.02801823228221075</v>
+        <v>0.01113987358445857</v>
       </c>
       <c r="D37">
-        <v>1.293311973586283</v>
+        <v>0.3306478977637105</v>
       </c>
       <c r="E37">
-        <v>0.1959031810984836</v>
+        <v>0.7409104620569897</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>Surgical Procedures, Operative</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1257,20 +1442,25 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.0834613258203635</v>
+        <v>-0.03873350276975595</v>
       </c>
       <c r="C38">
-        <v>0.04183367209723581</v>
+        <v>0.01743553607801604</v>
       </c>
       <c r="D38">
-        <v>-1.995075297869399</v>
+        <v>-2.221526346906757</v>
       </c>
       <c r="E38">
-        <v>0.04603466805827713</v>
+        <v>0.02631533224075729</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>Education</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -1281,20 +1471,25 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.0518726514508462</v>
+        <v>-0.01495858868782091</v>
       </c>
       <c r="C39">
-        <v>0.04741796853050215</v>
+        <v>0.01889467604101384</v>
       </c>
       <c r="D39">
-        <v>-1.093945039367904</v>
+        <v>-0.7916827287936011</v>
       </c>
       <c r="E39">
-        <v>0.2739790836585555</v>
+        <v>0.4285456953623846</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>Behavioral Disciplines and Activities</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1305,20 +1500,25 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.03466763767798526</v>
+        <v>-0.01976585557889786</v>
       </c>
       <c r="C40">
-        <v>0.04346281178554824</v>
+        <v>0.01772100643250281</v>
       </c>
       <c r="D40">
-        <v>-0.7976390908402421</v>
+        <v>-1.115391253548925</v>
       </c>
       <c r="E40">
-        <v>0.4250799593563103</v>
+        <v>0.2646827959756961</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>Cells</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1329,20 +1529,25 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.009997650603054586</v>
+        <v>-0.02463111038503147</v>
       </c>
       <c r="C41">
-        <v>0.02840430308113192</v>
+        <v>0.01207012953560481</v>
       </c>
       <c r="D41">
-        <v>0.3519766203908629</v>
+        <v>-2.040666615248322</v>
       </c>
       <c r="E41">
-        <v>0.7248557961796396</v>
+        <v>0.04128397586600612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>Cardiovascular Diseases</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -1353,20 +1558,25 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.04443389108037731</v>
+        <v>-0.003405795530291891</v>
       </c>
       <c r="C42">
-        <v>0.04115101553043655</v>
+        <v>0.01490272147422838</v>
       </c>
       <c r="D42">
-        <v>1.079776294889069</v>
+        <v>-0.2285351394496375</v>
       </c>
       <c r="E42">
-        <v>0.2802418096628149</v>
+        <v>0.8192302414785021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>Humanities</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1377,20 +1587,25 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.01793007754053122</v>
+        <v>-0.01104589261941247</v>
       </c>
       <c r="C43">
-        <v>0.04272558847584919</v>
+        <v>0.01795786228666845</v>
       </c>
       <c r="D43">
-        <v>0.4196566549496743</v>
+        <v>-0.6151006418850151</v>
       </c>
       <c r="E43">
-        <v>0.6747362940387691</v>
+        <v>0.538488258202014</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>Mental Disorders</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1401,20 +1616,25 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.05141154044563007</v>
+        <v>-0.009646757517610006</v>
       </c>
       <c r="C44">
-        <v>0.03840514608599255</v>
+        <v>0.01727662320125976</v>
       </c>
       <c r="D44">
-        <v>-1.338662801347378</v>
+        <v>-0.5583705452872637</v>
       </c>
       <c r="E44">
-        <v>0.1806804713243028</v>
+        <v>0.5765913817855483</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>Human Activities</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1425,20 +1645,25 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.01806974187274473</v>
+        <v>0.005719426911005579</v>
       </c>
       <c r="C45">
-        <v>0.0465454071425213</v>
+        <v>0.01874279209648068</v>
       </c>
       <c r="D45">
-        <v>0.3882175059166518</v>
+        <v>0.3051534094581091</v>
       </c>
       <c r="E45">
-        <v>0.6978550792994377</v>
+        <v>0.7602493149117824</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>Body Regions</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1449,20 +1674,25 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.08083318222183369</v>
+        <v>-0.06517740476827896</v>
       </c>
       <c r="C46">
-        <v>0.06788551917849446</v>
+        <v>0.02485782267989147</v>
       </c>
       <c r="D46">
-        <v>-1.190727907807486</v>
+        <v>-2.62200779238013</v>
       </c>
       <c r="E46">
-        <v>0.2337604183351377</v>
+        <v>0.008741343231672182</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>Infections</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>**</t>
         </is>
       </c>
     </row>
@@ -1473,20 +1703,25 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.09808052154725365</v>
+        <v>-0.004926343265352978</v>
       </c>
       <c r="C47">
-        <v>0.04622703513529001</v>
+        <v>0.01731356509074363</v>
       </c>
       <c r="D47">
-        <v>-2.121713435875933</v>
+        <v>-0.2845366185146208</v>
       </c>
       <c r="E47">
-        <v>0.0338618096505106</v>
+        <v>0.7759991756558706</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>Musculoskeletal System</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1497,20 +1732,25 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.04870502277551871</v>
+        <v>-0.06872441750547584</v>
       </c>
       <c r="C48">
-        <v>0.06455444184388058</v>
+        <v>0.02460190473445825</v>
       </c>
       <c r="D48">
-        <v>-0.7544798062588421</v>
+        <v>-2.793459215749996</v>
       </c>
       <c r="E48">
-        <v>0.4505611665462678</v>
+        <v>0.00521476043508152</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>Respiratory Tract Diseases</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>**</t>
         </is>
       </c>
     </row>
@@ -1521,20 +1761,25 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.03908850793715064</v>
+        <v>0.02612718094776566</v>
       </c>
       <c r="C49">
-        <v>0.04795172219472111</v>
+        <v>0.01784395551630362</v>
       </c>
       <c r="D49">
-        <v>0.8151637970044339</v>
+        <v>1.464203434260629</v>
       </c>
       <c r="E49">
-        <v>0.4149785576813574</v>
+        <v>0.1431383721697725</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>Inorganic Chemicals</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1545,20 +1790,25 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.06315703404322748</v>
+        <v>0.006111294785118076</v>
       </c>
       <c r="C50">
-        <v>0.04578740570476569</v>
+        <v>0.01730780304205899</v>
       </c>
       <c r="D50">
-        <v>1.379353843510158</v>
+        <v>0.3530947729337609</v>
       </c>
       <c r="E50">
-        <v>0.1677856829129034</v>
+        <v>0.7240173914288081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>Organic Chemicals</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1569,20 +1819,25 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.04687207045914749</v>
+        <v>-0.02016425427442703</v>
       </c>
       <c r="C51">
-        <v>0.03732364447586351</v>
+        <v>0.01612791237259593</v>
       </c>
       <c r="D51">
-        <v>1.25582780345737</v>
+        <v>-1.250270574925093</v>
       </c>
       <c r="E51">
-        <v>0.2091784087866492</v>
+        <v>0.2112007235226919</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>Biological Factors</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1593,20 +1848,25 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.09028198738838594</v>
+        <v>0.007580934698476749</v>
       </c>
       <c r="C52">
-        <v>0.04729635180635605</v>
+        <v>0.02003707329484139</v>
       </c>
       <c r="D52">
-        <v>1.908857320708891</v>
+        <v>0.3783454093781494</v>
       </c>
       <c r="E52">
-        <v>0.05628050000460433</v>
+        <v>0.7051740162448585</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>Metabolism</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1617,20 +1877,25 @@
         </is>
       </c>
       <c r="B53">
-        <v>-0.02811616405034375</v>
+        <v>-0.03122412491772363</v>
       </c>
       <c r="C53">
-        <v>0.05744821748518719</v>
+        <v>0.02468650594045579</v>
       </c>
       <c r="D53">
-        <v>-0.4894175186130605</v>
+        <v>-1.264825609303992</v>
       </c>
       <c r="E53">
-        <v>0.6245461358787404</v>
+        <v>0.2059338490009726</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>Cell Physiological Phenomena</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1641,20 +1906,25 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.08588185380877524</v>
+        <v>0.04434783606459209</v>
       </c>
       <c r="C54">
-        <v>0.04388491019127877</v>
+        <v>0.01481116203187692</v>
       </c>
       <c r="D54">
-        <v>1.956979140083611</v>
+        <v>2.99421719708053</v>
       </c>
       <c r="E54">
-        <v>0.05034992091992203</v>
+        <v>0.002751499981810517</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>Urogenital Diseases</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>**</t>
         </is>
       </c>
     </row>
@@ -1665,20 +1935,25 @@
         </is>
       </c>
       <c r="B55">
-        <v>-0.05468751106752658</v>
+        <v>0.001639198858233569</v>
       </c>
       <c r="C55">
-        <v>0.04617673385909195</v>
+        <v>0.01674579503105565</v>
       </c>
       <c r="D55">
-        <v>-1.184308774076686</v>
+        <v>0.09788719228878763</v>
       </c>
       <c r="E55">
-        <v>0.236290856871583</v>
+        <v>0.9220218702147521</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>Circulatory and Respiratory Physiological Phenomena</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1689,20 +1964,25 @@
         </is>
       </c>
       <c r="B56">
-        <v>-0.02024264903383842</v>
+        <v>0.001542221380103572</v>
       </c>
       <c r="C56">
-        <v>0.05039926575144194</v>
+        <v>0.01929891021276475</v>
       </c>
       <c r="D56">
-        <v>-0.401645713127463</v>
+        <v>0.07991235583258538</v>
       </c>
       <c r="E56">
-        <v>0.6879447821949736</v>
+        <v>0.9363069627262258</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>Tissues</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1713,20 +1993,25 @@
         </is>
       </c>
       <c r="B57">
-        <v>-0.02311531009958613</v>
+        <v>0.01321470254428619</v>
       </c>
       <c r="C57">
-        <v>0.0397260940094076</v>
+        <v>0.01425651098382922</v>
       </c>
       <c r="D57">
-        <v>-0.5818671751144766</v>
+        <v>0.9269240250489948</v>
       </c>
       <c r="E57">
-        <v>0.5606561520861491</v>
+        <v>0.3539659822712366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>Skin and Connective Tissue Diseases</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1737,20 +2022,25 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.1523370190552552</v>
+        <v>0.01242990750988507</v>
       </c>
       <c r="C58">
-        <v>0.06222068222917882</v>
+        <v>0.0219801348283024</v>
       </c>
       <c r="D58">
-        <v>2.448334116526542</v>
+        <v>0.5655064269159933</v>
       </c>
       <c r="E58">
-        <v>0.01435184994260604</v>
+        <v>0.5717293540920132</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>Nucleic Acids, Nucleotides, and Nucleosides</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1761,20 +2051,25 @@
         </is>
       </c>
       <c r="B59">
-        <v>-0.01060039059431308</v>
+        <v>-0.01516149119863781</v>
       </c>
       <c r="C59">
-        <v>0.05648389879917019</v>
+        <v>0.02193158530501762</v>
       </c>
       <c r="D59">
-        <v>-0.187671014566523</v>
+        <v>-0.6913084935619809</v>
       </c>
       <c r="E59">
-        <v>0.8511345535312747</v>
+        <v>0.4893716953392392</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>Reproductive and Urinary Physiological Phenomena</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1785,20 +2080,25 @@
         </is>
       </c>
       <c r="B60">
-        <v>0.04833596504479053</v>
+        <v>0.02692715267819313</v>
       </c>
       <c r="C60">
-        <v>0.04613355522390625</v>
+        <v>0.01678847469867301</v>
       </c>
       <c r="D60">
-        <v>1.047739867655875</v>
+        <v>1.603907035123417</v>
       </c>
       <c r="E60">
-        <v>0.2947584739621865</v>
+        <v>0.1087345458804685</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>Digestive System Diseases</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1809,20 +2109,25 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.005207414983186833</v>
+        <v>-0.01738909065479892</v>
       </c>
       <c r="C61">
-        <v>0.04283961633142896</v>
+        <v>0.01751832237555035</v>
       </c>
       <c r="D61">
-        <v>0.1215560602340514</v>
+        <v>-0.9926230538529307</v>
       </c>
       <c r="E61">
-        <v>0.9032506141995033</v>
+        <v>0.3208936856369837</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>Cardiovascular System</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1833,20 +2138,25 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.009155916098225291</v>
+        <v>0.03725202060046567</v>
       </c>
       <c r="C62">
-        <v>0.04388316653085911</v>
+        <v>0.01626144430002977</v>
       </c>
       <c r="D62">
-        <v>0.208643013301849</v>
+        <v>2.290818694400809</v>
       </c>
       <c r="E62">
-        <v>0.8347269297034372</v>
+        <v>0.02197390195607278</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>Nutritional and Metabolic Diseases</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -1857,20 +2167,25 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.0133435778746938</v>
+        <v>-0.01471321246113828</v>
       </c>
       <c r="C63">
-        <v>0.04501722468685764</v>
+        <v>0.0175553568209564</v>
       </c>
       <c r="D63">
-        <v>0.2964104954828397</v>
+        <v>-0.838103868306148</v>
       </c>
       <c r="E63">
-        <v>0.7669166110420925</v>
+        <v>0.4019723705590987</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>Immune System Diseases</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1881,20 +2196,25 @@
         </is>
       </c>
       <c r="B64">
-        <v>-0.03927943290006835</v>
+        <v>-0.01135662008378118</v>
       </c>
       <c r="C64">
-        <v>0.07492439809273017</v>
+        <v>0.02827282753104204</v>
       </c>
       <c r="D64">
-        <v>-0.5242542336003042</v>
+        <v>-0.4016796718089913</v>
       </c>
       <c r="E64">
-        <v>0.6001017242319048</v>
+        <v>0.687919786922036</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>Ocular Physiological Phenomena</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1905,20 +2225,25 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.0272774784357135</v>
+        <v>-0.005040343586612712</v>
       </c>
       <c r="C65">
-        <v>0.07487926951633539</v>
+        <v>0.02614998731436411</v>
       </c>
       <c r="D65">
-        <v>0.3642861183329619</v>
+        <v>-0.1927474581926112</v>
       </c>
       <c r="E65">
-        <v>0.7156443647486372</v>
+        <v>0.8471567540252658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>Enzymes and Coenzymes</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1929,20 +2254,25 @@
         </is>
       </c>
       <c r="B66">
-        <v>0.09850945408065989</v>
+        <v>0.02200645697938469</v>
       </c>
       <c r="C66">
-        <v>0.06014374299818579</v>
+        <v>0.02078999214069062</v>
       </c>
       <c r="D66">
-        <v>1.637900289704806</v>
+        <v>1.058512039372693</v>
       </c>
       <c r="E66">
-        <v>0.1014424955352468</v>
+        <v>0.2898220649138185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>Carbohydrates</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1953,20 +2283,25 @@
         </is>
       </c>
       <c r="B67">
-        <v>0.04700853769476554</v>
+        <v>0.03520633393132249</v>
       </c>
       <c r="C67">
-        <v>0.05055449484184408</v>
+        <v>0.01816924792501195</v>
       </c>
       <c r="D67">
-        <v>0.9298587166547347</v>
+        <v>1.937688014199924</v>
       </c>
       <c r="E67">
-        <v>0.3524442403156001</v>
+        <v>0.05266129711349594</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>Endocrine System Diseases</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1977,20 +2312,25 @@
         </is>
       </c>
       <c r="B68">
-        <v>-0.09971243987932131</v>
+        <v>-0.053794376843204</v>
       </c>
       <c r="C68">
-        <v>0.07324877878896931</v>
+        <v>0.03123901818002648</v>
       </c>
       <c r="D68">
-        <v>-1.361284672971739</v>
+        <v>-1.72202521004962</v>
       </c>
       <c r="E68">
-        <v>0.173423744715013</v>
+        <v>0.08506495180893082</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>Eye Diseases</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2001,20 +2341,25 @@
         </is>
       </c>
       <c r="B69">
-        <v>-0.1126168196692887</v>
+        <v>-0.0133359730370928</v>
       </c>
       <c r="C69">
-        <v>0.06839580305001366</v>
+        <v>0.02462177306906094</v>
       </c>
       <c r="D69">
-        <v>-1.646545762273439</v>
+        <v>-0.5416333340286703</v>
       </c>
       <c r="E69">
-        <v>0.09965144653842803</v>
+        <v>0.5880711235802255</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>Musculoskeletal Diseases</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2025,20 +2370,25 @@
         </is>
       </c>
       <c r="B70">
-        <v>-0.3466110666074054</v>
+        <v>-0.03289269977608875</v>
       </c>
       <c r="C70">
-        <v>0.1653196962944084</v>
+        <v>0.04109028454945858</v>
       </c>
       <c r="D70">
-        <v>-2.096610835711587</v>
+        <v>-0.8004982232843203</v>
       </c>
       <c r="E70">
-        <v>0.03602803928973818</v>
+        <v>0.4234221925446589</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>Viruses</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2049,20 +2399,25 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.001138934626869513</v>
+        <v>-0.006112116703381947</v>
       </c>
       <c r="C71">
-        <v>0.05956606487531499</v>
+        <v>0.02188129039610121</v>
       </c>
       <c r="D71">
-        <v>0.0191205282614112</v>
+        <v>-0.2793307246848202</v>
       </c>
       <c r="E71">
-        <v>0.9847449552384889</v>
+        <v>0.7799910294092394</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>Heterocyclic Compounds</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2073,20 +2428,25 @@
         </is>
       </c>
       <c r="B72">
-        <v>0.01910931183419166</v>
+        <v>0.002381040046268487</v>
       </c>
       <c r="C72">
-        <v>0.06868525090237702</v>
+        <v>0.02635544148260659</v>
       </c>
       <c r="D72">
-        <v>0.2782156515865669</v>
+        <v>0.09034339446902707</v>
       </c>
       <c r="E72">
-        <v>0.7808468207580832</v>
+        <v>0.9280143373186616</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>Wounds and Injuries</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2097,20 +2457,25 @@
         </is>
       </c>
       <c r="B73">
-        <v>0.01615749296890108</v>
+        <v>-0.03072487188857212</v>
       </c>
       <c r="C73">
-        <v>0.08305129935516715</v>
+        <v>0.03518191645595382</v>
       </c>
       <c r="D73">
-        <v>0.1945483465563121</v>
+        <v>-0.8733143325787347</v>
       </c>
       <c r="E73">
-        <v>0.8457465437272673</v>
+        <v>0.3824917705056879</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>Sense Organs</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2121,20 +2486,25 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.01232609605773012</v>
+        <v>0.0428984697431363</v>
       </c>
       <c r="C74">
-        <v>0.0747777783479576</v>
+        <v>0.02764738962179463</v>
       </c>
       <c r="D74">
-        <v>0.1648363501837946</v>
+        <v>1.551628212643958</v>
       </c>
       <c r="E74">
-        <v>0.8690727920653363</v>
+        <v>0.1207512085544296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>Complex Mixtures</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2145,20 +2515,25 @@
         </is>
       </c>
       <c r="B75">
-        <v>0.03334511371370298</v>
+        <v>0.02287847406590389</v>
       </c>
       <c r="C75">
-        <v>0.07623120104683918</v>
+        <v>0.02542660472023226</v>
       </c>
       <c r="D75">
-        <v>0.4374208100593161</v>
+        <v>0.8997848638319847</v>
       </c>
       <c r="E75">
-        <v>0.6618061949017122</v>
+        <v>0.3682347508992462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>Bacteria</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2169,20 +2544,25 @@
         </is>
       </c>
       <c r="B76">
-        <v>-0.01761004906174436</v>
+        <v>0.008490649281633971</v>
       </c>
       <c r="C76">
-        <v>0.07258271959104057</v>
+        <v>0.02487233841409021</v>
       </c>
       <c r="D76">
-        <v>-0.2426204082867969</v>
+        <v>0.3413691604012596</v>
       </c>
       <c r="E76">
-        <v>0.8082994699938469</v>
+        <v>0.7328256886608278</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>Congenital, Hereditary, and Neonatal Diseases and Abnormalities</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2193,20 +2573,25 @@
         </is>
       </c>
       <c r="B77">
-        <v>-0.01082390713240928</v>
+        <v>-0.0268527095434924</v>
       </c>
       <c r="C77">
-        <v>0.0740861183044404</v>
+        <v>0.03420675972754205</v>
       </c>
       <c r="D77">
-        <v>-0.1460989910138205</v>
+        <v>-0.7850117858977319</v>
       </c>
       <c r="E77">
-        <v>0.8838432429254832</v>
+        <v>0.432446658418302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>Non-Medical Public and Private Facilities</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2217,20 +2602,25 @@
         </is>
       </c>
       <c r="B78">
-        <v>-0.07668259149293739</v>
+        <v>-0.01654895098181839</v>
       </c>
       <c r="C78">
-        <v>0.06124266100492742</v>
+        <v>0.02627077905052425</v>
       </c>
       <c r="D78">
-        <v>-1.252110705750812</v>
+        <v>-0.6299375800767563</v>
       </c>
       <c r="E78">
-        <v>0.2105295272063894</v>
+        <v>0.5287354242649631</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>Food and Beverages</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2241,20 +2631,25 @@
         </is>
       </c>
       <c r="B79">
-        <v>0.006120465648860748</v>
+        <v>0.01012928721046699</v>
       </c>
       <c r="C79">
-        <v>0.07277320765239455</v>
+        <v>0.02945140730858157</v>
       </c>
       <c r="D79">
-        <v>0.08410328259949057</v>
+        <v>0.3439321966633329</v>
       </c>
       <c r="E79">
-        <v>0.9329743147563835</v>
+        <v>0.7308972778346581</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>Pharmaceutical Preparations</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2265,20 +2660,25 @@
         </is>
       </c>
       <c r="B80">
-        <v>-0.08958333174236058</v>
+        <v>0.01870580741975258</v>
       </c>
       <c r="C80">
-        <v>0.07147782302096573</v>
+        <v>0.02579523960774362</v>
       </c>
       <c r="D80">
-        <v>-1.253302464403318</v>
+        <v>0.7251650965140553</v>
       </c>
       <c r="E80">
-        <v>0.210095651916947</v>
+        <v>0.4683507526966605</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>Digestive System</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2289,20 +2689,25 @@
         </is>
       </c>
       <c r="B81">
-        <v>0.05970421367495871</v>
+        <v>0.04643164127335257</v>
       </c>
       <c r="C81">
-        <v>0.08298710408762459</v>
+        <v>0.0263509239403135</v>
       </c>
       <c r="D81">
-        <v>0.7194396566955523</v>
+        <v>1.762049838499901</v>
       </c>
       <c r="E81">
-        <v>0.4718700699305466</v>
+        <v>0.078060877306945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>Macromolecular Substances</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2313,20 +2718,25 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.0591291504000978</v>
+        <v>0.006411252192304921</v>
       </c>
       <c r="C82">
-        <v>0.09033868069582464</v>
+        <v>0.03234616734986337</v>
       </c>
       <c r="D82">
-        <v>0.6545274952507768</v>
+        <v>0.1982074761117565</v>
       </c>
       <c r="E82">
-        <v>0.5127720189452389</v>
+        <v>0.8428827384365515</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>Otorhinolaryngologic Diseases</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2337,20 +2747,25 @@
         </is>
       </c>
       <c r="B83">
-        <v>0.05503490972275302</v>
+        <v>0.005961482651921807</v>
       </c>
       <c r="C83">
-        <v>0.05772070807354805</v>
+        <v>0.02049815692105954</v>
       </c>
       <c r="D83">
-        <v>0.9534690678539014</v>
+        <v>0.2908301792634369</v>
       </c>
       <c r="E83">
-        <v>0.3403524613275524</v>
+        <v>0.7711812027921534</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>Dentistry</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2361,20 +2776,25 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.1992577128817652</v>
+        <v>-0.02807860411730743</v>
       </c>
       <c r="C84">
-        <v>0.09633291034224999</v>
+        <v>0.03870927211490294</v>
       </c>
       <c r="D84">
-        <v>2.068428247146751</v>
+        <v>-0.7253715346018419</v>
       </c>
       <c r="E84">
-        <v>0.03859977131426088</v>
+        <v>0.4682241312206358</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>Chemically-Induced Disorders</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2385,20 +2805,25 @@
         </is>
       </c>
       <c r="B85">
-        <v>0.1455091740843895</v>
+        <v>0.03575935139720798</v>
       </c>
       <c r="C85">
-        <v>0.08395686993233027</v>
+        <v>0.02945405048157959</v>
       </c>
       <c r="D85">
-        <v>1.733141959695148</v>
+        <v>1.214072455656708</v>
       </c>
       <c r="E85">
-        <v>0.08307044004036593</v>
+        <v>0.2247200571268456</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
           <t>Urogenital System</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2409,20 +2834,25 @@
         </is>
       </c>
       <c r="B86">
-        <v>0.03105221005979415</v>
+        <v>0.03206293127076798</v>
       </c>
       <c r="C86">
-        <v>0.07340618621202748</v>
+        <v>0.02565285796672443</v>
       </c>
       <c r="D86">
-        <v>0.4230189805815889</v>
+        <v>1.249877550187912</v>
       </c>
       <c r="E86">
-        <v>0.672281412840108</v>
+        <v>0.2113442814494319</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>Biomedical and Dental Materials</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2433,20 +2863,25 @@
         </is>
       </c>
       <c r="B87">
-        <v>-0.01211203066462792</v>
+        <v>-0.04717462095163126</v>
       </c>
       <c r="C87">
-        <v>0.08880091811008288</v>
+        <v>0.03714814950199456</v>
       </c>
       <c r="D87">
-        <v>-0.1363953315168784</v>
+        <v>-1.269905004261339</v>
       </c>
       <c r="E87">
-        <v>0.8915087640998987</v>
+        <v>0.2041184704023702</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>Hemic and Immune Systems</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2457,20 +2892,25 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.02571214473878232</v>
+        <v>-0.01716842137604305</v>
       </c>
       <c r="C88">
-        <v>0.0717868543506338</v>
+        <v>0.02826836892831558</v>
       </c>
       <c r="D88">
-        <v>0.3581734423574908</v>
+        <v>-0.6073368229903762</v>
       </c>
       <c r="E88">
-        <v>0.7202135205440697</v>
+        <v>0.5436274058752903</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>Stomatognathic System</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2481,20 +2921,25 @@
         </is>
       </c>
       <c r="B89">
-        <v>-0.03459667878918488</v>
+        <v>-0.03757223864915468</v>
       </c>
       <c r="C89">
-        <v>0.096665582729733</v>
+        <v>0.04182585625768164</v>
       </c>
       <c r="D89">
-        <v>-0.3579006903202934</v>
+        <v>-0.8983017207747959</v>
       </c>
       <c r="E89">
-        <v>0.7204176340963897</v>
+        <v>0.3690247154020383</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>Respiratory System</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2505,20 +2950,25 @@
         </is>
       </c>
       <c r="B90">
-        <v>0.05040569588456804</v>
+        <v>-0.05307926915131607</v>
       </c>
       <c r="C90">
-        <v>0.05818746658482565</v>
+        <v>0.02631416981078992</v>
       </c>
       <c r="D90">
-        <v>0.8662637994573392</v>
+        <v>-2.017136376825817</v>
       </c>
       <c r="E90">
-        <v>0.3863455134425163</v>
+        <v>0.04368128337029357</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>Stomatognathic Diseases</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -2529,20 +2979,25 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.03859432386454533</v>
+        <v>-0.03221302281359465</v>
       </c>
       <c r="C91">
-        <v>0.1244455222458587</v>
+        <v>0.05859645254531656</v>
       </c>
       <c r="D91">
-        <v>0.3101302736172147</v>
+        <v>-0.5497435666209002</v>
       </c>
       <c r="E91">
-        <v>0.7564618914314272</v>
+        <v>0.5824952704817472</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>Microbiological Phenomena</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2553,20 +3008,25 @@
         </is>
       </c>
       <c r="B92">
-        <v>-0.1629239232066866</v>
+        <v>-0.01352438988658443</v>
       </c>
       <c r="C92">
-        <v>0.0923514088858693</v>
+        <v>0.031268426126836</v>
       </c>
       <c r="D92">
-        <v>-1.764173662017793</v>
+        <v>-0.4325254437727258</v>
       </c>
       <c r="E92">
-        <v>0.07770274560148213</v>
+        <v>0.665359563765066</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>Polycyclic Compounds</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2577,20 +3037,25 @@
         </is>
       </c>
       <c r="B93">
-        <v>-0.02171540073722777</v>
+        <v>0.0035550710185448</v>
       </c>
       <c r="C93">
-        <v>0.08033160149938594</v>
+        <v>0.03043871471166251</v>
       </c>
       <c r="D93">
-        <v>-0.27032201937856</v>
+        <v>0.1167943867611034</v>
       </c>
       <c r="E93">
-        <v>0.7869125267154011</v>
+        <v>0.9070229920246901</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
           <t>Lipids</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2601,20 +3066,25 @@
         </is>
       </c>
       <c r="B94">
-        <v>0.05213573155174272</v>
+        <v>0.07912881590207843</v>
       </c>
       <c r="C94">
-        <v>0.1753349212803905</v>
+        <v>0.05354111637893777</v>
       </c>
       <c r="D94">
-        <v>0.2973493880797925</v>
+        <v>1.477907470999362</v>
       </c>
       <c r="E94">
-        <v>0.7661997795059906</v>
+        <v>0.1394325463578538</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>Plant Structures</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2625,20 +3095,25 @@
         </is>
       </c>
       <c r="B95">
-        <v>0.2423748947416301</v>
+        <v>0.04258385401187061</v>
       </c>
       <c r="C95">
-        <v>0.10218885632603</v>
+        <v>0.03137862296027136</v>
       </c>
       <c r="D95">
-        <v>2.371832932236186</v>
+        <v>1.357097603224534</v>
       </c>
       <c r="E95">
-        <v>0.01770009209682163</v>
+        <v>0.1747501999354673</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
           <t>Hemic and Lymphatic Diseases</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2649,20 +3124,25 @@
         </is>
       </c>
       <c r="B96">
-        <v>-0.2499415149288737</v>
+        <v>-0.08145724227900997</v>
       </c>
       <c r="C96">
-        <v>0.1304468671569541</v>
+        <v>0.0542561535212629</v>
       </c>
       <c r="D96">
-        <v>-1.91604076338716</v>
+        <v>-1.501345690624512</v>
       </c>
       <c r="E96">
-        <v>0.05535990728720262</v>
+        <v>0.1332661729896425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
           <t>Animal Diseases</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2673,20 +3153,25 @@
         </is>
       </c>
       <c r="B97">
-        <v>-0.02805263450066155</v>
+        <v>0.0204047569332843</v>
       </c>
       <c r="C97">
-        <v>0.08855577845933503</v>
+        <v>0.02846018096971155</v>
       </c>
       <c r="D97">
-        <v>-0.3167792660028772</v>
+        <v>0.7169580880388585</v>
       </c>
       <c r="E97">
-        <v>0.7514110979187095</v>
+        <v>0.4733999580314429</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
           <t>Hormones, Hormone Substitutes, and Hormone Antagonists</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2697,20 +3182,25 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.1143467620031016</v>
+        <v>0.05918264525536058</v>
       </c>
       <c r="C98">
-        <v>0.1341948605845031</v>
+        <v>0.03825588041385347</v>
       </c>
       <c r="D98">
-        <v>0.8520949424221576</v>
+        <v>1.54702086620725</v>
       </c>
       <c r="E98">
-        <v>0.3941613988328083</v>
+        <v>0.1218582141437474</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>Fluids and Secretions</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2721,20 +3211,25 @@
         </is>
       </c>
       <c r="B99">
-        <v>0.1095997100662882</v>
+        <v>-0.02996244954050826</v>
       </c>
       <c r="C99">
-        <v>0.1131703007830765</v>
+        <v>0.04258651272696497</v>
       </c>
       <c r="D99">
-        <v>0.9684494015472102</v>
+        <v>-0.7035666369915423</v>
       </c>
       <c r="E99">
-        <v>0.3328199773881157</v>
+        <v>0.4817026944937913</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>Immune System Phenomena</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2745,20 +3240,25 @@
         </is>
       </c>
       <c r="B100">
-        <v>-0.1061097293960335</v>
+        <v>0.04796040423913991</v>
       </c>
       <c r="C100">
-        <v>0.1397868602855034</v>
+        <v>0.04497957800059426</v>
       </c>
       <c r="D100">
-        <v>-0.7590822855546866</v>
+        <v>1.066270658175278</v>
       </c>
       <c r="E100">
-        <v>0.4478033351906279</v>
+        <v>0.286301309368579</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>Integumentary System</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2769,20 +3269,25 @@
         </is>
       </c>
       <c r="B101">
-        <v>-0.07411219448420607</v>
+        <v>-0.04286355145130385</v>
       </c>
       <c r="C101">
-        <v>0.1208078008488535</v>
+        <v>0.04814595654200803</v>
       </c>
       <c r="D101">
-        <v>-0.613471927834612</v>
+        <v>-0.8902835155825555</v>
       </c>
       <c r="E101">
-        <v>0.5395643389849182</v>
+        <v>0.3733136702274715</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>Embryonic Structures</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2793,20 +3298,25 @@
         </is>
       </c>
       <c r="B102">
-        <v>0.1527906422293685</v>
+        <v>0.03467794734113636</v>
       </c>
       <c r="C102">
-        <v>0.1814879447129475</v>
+        <v>0.06853510374555385</v>
       </c>
       <c r="D102">
-        <v>0.8418776380493568</v>
+        <v>0.5059881060351654</v>
       </c>
       <c r="E102">
-        <v>0.3998564485117572</v>
+        <v>0.6128649993588547</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
           <t>Organism Forms</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2817,20 +3327,25 @@
         </is>
       </c>
       <c r="B103">
-        <v>-0.05544232099538679</v>
+        <v>0.001613121896286533</v>
       </c>
       <c r="C103">
-        <v>0.2034413062419288</v>
+        <v>0.07623397235260483</v>
       </c>
       <c r="D103">
-        <v>-0.2725224391228385</v>
+        <v>0.02116014483444945</v>
       </c>
       <c r="E103">
-        <v>0.7852203400418981</v>
+        <v>0.9831179069726989</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
           <t>Animal Structures</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2841,20 +3356,25 @@
         </is>
       </c>
       <c r="B104">
-        <v>-0.2431145250842237</v>
+        <v>-0.03009068304027159</v>
       </c>
       <c r="C104">
-        <v>0.1744390224093005</v>
+        <v>0.05555224393405486</v>
       </c>
       <c r="D104">
-        <v>-1.393693462198981</v>
+        <v>-0.5416645829103094</v>
       </c>
       <c r="E104">
-        <v>0.1634101913331394</v>
+        <v>0.5880495924363743</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
           <t>Occupational Diseases</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2865,20 +3385,25 @@
         </is>
       </c>
       <c r="B105">
-        <v>-0.01482693010670843</v>
+        <v>-0.01976404335429352</v>
       </c>
       <c r="C105">
-        <v>0.08826322313557738</v>
+        <v>0.03681149674366985</v>
       </c>
       <c r="D105">
-        <v>-0.1679853689903598</v>
+        <v>-0.5368986621738538</v>
       </c>
       <c r="E105">
-        <v>0.8665947893651789</v>
+        <v>0.5913376151640194</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
           <t>Digestive System and Oral Physiological Phenomena</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2889,20 +3414,25 @@
         </is>
       </c>
       <c r="B106">
-        <v>-0.07198386066618914</v>
+        <v>-0.02963882318458224</v>
       </c>
       <c r="C106">
-        <v>0.1811844401532959</v>
+        <v>0.0772806198845872</v>
       </c>
       <c r="D106">
-        <v>-0.3972960404617818</v>
+        <v>-0.3835220683897928</v>
       </c>
       <c r="E106">
-        <v>0.6911491668836574</v>
+        <v>0.7013327106563028</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
           <t>Plant Physiological Phenomena</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2913,20 +3443,25 @@
         </is>
       </c>
       <c r="B107">
-        <v>0.2855954039151104</v>
+        <v>0.02045335838234351</v>
       </c>
       <c r="C107">
-        <v>0.1818428700451172</v>
+        <v>0.06435171445159397</v>
       </c>
       <c r="D107">
-        <v>1.570561462455202</v>
+        <v>0.3178370391006247</v>
       </c>
       <c r="E107">
-        <v>0.1162845473739926</v>
+        <v>0.7506085532626532</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
           <t>Integumentary System Physiological Phenomena</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2937,20 +3472,25 @@
         </is>
       </c>
       <c r="B108">
-        <v>-0.1809553600693732</v>
+        <v>-0.2487945460937678</v>
       </c>
       <c r="C108">
-        <v>0.3809484631119274</v>
+        <v>0.2986450037349527</v>
       </c>
       <c r="D108">
-        <v>-0.4750127053700865</v>
+        <v>-0.8330778783581217</v>
       </c>
       <c r="E108">
-        <v>0.6347779173698729</v>
+        <v>0.4048008088397569</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
           <t>Anesthesia and Analgesia</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2961,20 +3501,25 @@
         </is>
       </c>
       <c r="B109">
-        <v>0.1730459701622066</v>
+        <v>-0.005329292883944292</v>
       </c>
       <c r="C109">
-        <v>0.1382855848641468</v>
+        <v>0.04985154456759455</v>
       </c>
       <c r="D109">
-        <v>1.251366657863933</v>
+        <v>-0.106903265087769</v>
       </c>
       <c r="E109">
-        <v>0.2108007360578089</v>
+        <v>0.9148657228722145</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>Endocrine System</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2985,20 +3530,25 @@
         </is>
       </c>
       <c r="B110">
-        <v>-0.2871419197313733</v>
+        <v>-0.05739590309520964</v>
       </c>
       <c r="C110">
-        <v>0.3279939501470774</v>
+        <v>0.1038029826159342</v>
       </c>
       <c r="D110">
-        <v>-0.87544882947571</v>
+        <v>-0.5529311552402265</v>
       </c>
       <c r="E110">
-        <v>0.3813297410566622</v>
+        <v>0.5803105527795019</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>Bacterial Structures</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -3009,20 +3559,25 @@
         </is>
       </c>
       <c r="B111">
-        <v>-0.007843959594657444</v>
+        <v>0.1975783391763166</v>
       </c>
       <c r="C111">
-        <v>4651.26003603445</v>
+        <v>0.1272107305521095</v>
       </c>
       <c r="D111">
-        <v>-1.686416053690478E-06</v>
+        <v>1.553157806097045</v>
       </c>
       <c r="E111">
-        <v>0.9999986544346676</v>
+        <v>0.1203854388109779</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
           <t>Archaea</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -3033,20 +3588,25 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.05328203274619683</v>
+        <v>0.04719706284783509</v>
       </c>
       <c r="C112">
-        <v>4651.259957019603</v>
+        <v>923.43211191486</v>
       </c>
       <c r="D112">
-        <v>1.145539772847666E-05</v>
+        <v>5.111048472200698E-05</v>
       </c>
       <c r="E112">
-        <v>0.9999908599150148</v>
+        <v>0.9999592197333629</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
           <t>Viral Structures</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -3057,20 +3617,25 @@
         </is>
       </c>
       <c r="B113">
-        <v>0.01684572214165758</v>
+        <v>0.0226267122492961</v>
       </c>
       <c r="C113">
-        <v>154032.2213957847</v>
+        <v>83126.49089812193</v>
       </c>
       <c r="D113">
-        <v>1.093649237088688E-07</v>
+        <v>2.721961676095159E-07</v>
       </c>
       <c r="E113">
-        <v>0.9999999127394159</v>
+        <v>0.9999997828188804</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>Fungal Structures</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -3081,20 +3646,25 @@
         </is>
       </c>
       <c r="B114">
-        <v>-0.06114593850907203</v>
+        <v>-0.03143608820381232</v>
       </c>
       <c r="C114">
-        <v>3019.84107573403</v>
+        <v>1023.785691558143</v>
       </c>
       <c r="D114">
-        <v>-2.024806503905486E-05</v>
+        <v>-3.070573115352727E-05</v>
       </c>
       <c r="E114">
-        <v>0.9999838443815203</v>
+        <v>0.9999755003711883</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
           <t>Disorders of Environmental Origin</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>

--- a/output/tables/mesh/experiment_2/stats-level_glm_level1.xlsx
+++ b/output/tables/mesh/experiment_2/stats-level_glm_level1.xlsx
@@ -398,16 +398,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.008475714782482401</v>
+        <v>0.004123741281820789</v>
       </c>
       <c r="C2">
-        <v>0.00513320456866282</v>
+        <v>0.01171245002045036</v>
       </c>
       <c r="D2">
-        <v>-1.651154686923045</v>
+        <v>0.3520818679798494</v>
       </c>
       <c r="E2">
-        <v>0.09870699301225966</v>
+        <v>0.7247768661375179</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -427,16 +427,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.005755412148764353</v>
+        <v>0.01073059245635813</v>
       </c>
       <c r="C3">
-        <v>0.008485518683350741</v>
+        <v>0.01159398489439228</v>
       </c>
       <c r="D3">
-        <v>-0.6782628574086964</v>
+        <v>0.92553100198951</v>
       </c>
       <c r="E3">
-        <v>0.4976050443098779</v>
+        <v>0.3546897651527066</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -456,16 +456,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.003608591230488276</v>
+        <v>0.007624668651695395</v>
       </c>
       <c r="C4">
-        <v>0.008254034019105076</v>
+        <v>0.01343203348155087</v>
       </c>
       <c r="D4">
-        <v>-0.4371912233625043</v>
+        <v>0.5676481273046265</v>
       </c>
       <c r="E4">
-        <v>0.6619726742207138</v>
+        <v>0.5702739207297273</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -485,16 +485,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.003216532824229183</v>
+        <v>0.01191806275939768</v>
       </c>
       <c r="C5">
-        <v>0.007989481986750147</v>
+        <v>0.01488104194446039</v>
       </c>
       <c r="D5">
-        <v>0.402595916676891</v>
+        <v>0.8008889971467545</v>
       </c>
       <c r="E5">
-        <v>0.6872455140610555</v>
+        <v>0.4231959104217797</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.00832094252732707</v>
+        <v>0.003252708562625903</v>
       </c>
       <c r="C6">
-        <v>0.008343613309927807</v>
+        <v>0.01286397837009484</v>
       </c>
       <c r="D6">
-        <v>-0.997282857946717</v>
+        <v>0.2528540136687063</v>
       </c>
       <c r="E6">
-        <v>0.3186272319594334</v>
+        <v>0.8003810266514355</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.01325485087409543</v>
+        <v>0.02247756224779169</v>
       </c>
       <c r="C7">
-        <v>0.006653767638158191</v>
+        <v>0.01436130639217183</v>
       </c>
       <c r="D7">
-        <v>1.992082019528482</v>
+        <v>1.565147461796647</v>
       </c>
       <c r="E7">
-        <v>0.04636205943448692</v>
+        <v>0.1175483371100745</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.0004464322779452414</v>
+        <v>0.01562432421494659</v>
       </c>
       <c r="C8">
-        <v>0.00659727202452429</v>
+        <v>0.01548986811254355</v>
       </c>
       <c r="D8">
-        <v>0.06766922392857255</v>
+        <v>1.008680261279575</v>
       </c>
       <c r="E8">
-        <v>0.9460489488821552</v>
+        <v>0.3131280011653594</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.0131956419735254</v>
+        <v>0.02363319396905329</v>
       </c>
       <c r="C9">
-        <v>0.007794645234987047</v>
+        <v>0.0178696601642707</v>
       </c>
       <c r="D9">
-        <v>1.692911168592438</v>
+        <v>1.322531808204525</v>
       </c>
       <c r="E9">
-        <v>0.09047237711414877</v>
+        <v>0.1859911246710405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -630,16 +630,16 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.02193670413617474</v>
+        <v>0.03651974466261174</v>
       </c>
       <c r="C10">
-        <v>0.009991148191344567</v>
+        <v>0.0213509041924521</v>
       </c>
       <c r="D10">
-        <v>2.195613929055594</v>
+        <v>1.7104542427539</v>
       </c>
       <c r="E10">
-        <v>0.02811958840738123</v>
+        <v>0.08718190788260462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.001880757629575273</v>
+        <v>0.004583367999737158</v>
       </c>
       <c r="C11">
-        <v>0.008551963756664069</v>
+        <v>0.01916512968752853</v>
       </c>
       <c r="D11">
-        <v>0.2199211412828666</v>
+        <v>0.2391514210686363</v>
       </c>
       <c r="E11">
-        <v>0.8259325709979959</v>
+        <v>0.8109881701042466</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -688,16 +688,16 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.02999636738569342</v>
+        <v>-0.03120504480597159</v>
       </c>
       <c r="C12">
-        <v>0.0107144620357381</v>
+        <v>0.02312651469386715</v>
       </c>
       <c r="D12">
-        <v>-2.799614883662894</v>
+        <v>-1.349318962197394</v>
       </c>
       <c r="E12">
-        <v>0.005116360688462788</v>
+        <v>0.177234537529861</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -717,16 +717,16 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.02742558946750381</v>
+        <v>-0.03418326250020366</v>
       </c>
       <c r="C13">
-        <v>0.01059666237667933</v>
+        <v>0.02340314686933305</v>
       </c>
       <c r="D13">
-        <v>-2.58813468737674</v>
+        <v>-1.460626756352866</v>
       </c>
       <c r="E13">
-        <v>0.00964972413076428</v>
+        <v>0.1441178993525119</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.01291616183164804</v>
+        <v>0.01194975634774235</v>
       </c>
       <c r="C14">
-        <v>0.01164029566412912</v>
+        <v>0.02078953105729803</v>
       </c>
       <c r="D14">
-        <v>-1.1096077113789</v>
+        <v>0.5747968203230568</v>
       </c>
       <c r="E14">
-        <v>0.2671681068610686</v>
+        <v>0.5654287174508092</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.0171790576601876</v>
+        <v>-0.01769951259126079</v>
       </c>
       <c r="C15">
-        <v>0.008907699607862786</v>
+        <v>0.02158571465818489</v>
       </c>
       <c r="D15">
-        <v>-1.928562750928839</v>
+        <v>-0.8199641694304282</v>
       </c>
       <c r="E15">
-        <v>0.05378516704089294</v>
+        <v>0.4122365335018406</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.0156350052890929</v>
+        <v>-0.009795923921687431</v>
       </c>
       <c r="C16">
-        <v>0.009043192300733081</v>
+        <v>0.02224732315120452</v>
       </c>
       <c r="D16">
-        <v>-1.728925446805489</v>
+        <v>-0.4403192175125598</v>
       </c>
       <c r="E16">
-        <v>0.08382243906084788</v>
+        <v>0.6597059239682541</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -833,16 +833,16 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.01101502421913512</v>
+        <v>0.007371212942647956</v>
       </c>
       <c r="C17">
-        <v>0.009992456481968469</v>
+        <v>0.02493979223860967</v>
       </c>
       <c r="D17">
-        <v>-1.102333969531105</v>
+        <v>0.295560318711736</v>
       </c>
       <c r="E17">
-        <v>0.2703165064149065</v>
+        <v>0.7675658814175612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -862,16 +862,16 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.01322506611329016</v>
+        <v>-0.01989376065099961</v>
       </c>
       <c r="C18">
-        <v>0.01137435114140975</v>
+        <v>0.02433580196398598</v>
       </c>
       <c r="D18">
-        <v>-1.162709498666931</v>
+        <v>-0.8174688748881156</v>
       </c>
       <c r="E18">
-        <v>0.2449473864388725</v>
+        <v>0.4136605294466743</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.001974438859813122</v>
+        <v>0.01787263686569638</v>
       </c>
       <c r="C19">
-        <v>0.01183145973347626</v>
+        <v>0.02462965494060864</v>
       </c>
       <c r="D19">
-        <v>0.166880410726209</v>
+        <v>0.7256551871633615</v>
       </c>
       <c r="E19">
-        <v>0.8674641469710436</v>
+        <v>0.4680501801699647</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.02400490242813999</v>
+        <v>-0.0502893212275629</v>
       </c>
       <c r="C20">
-        <v>0.01122694067493862</v>
+        <v>0.02686365969364507</v>
       </c>
       <c r="D20">
-        <v>-2.138151712311531</v>
+        <v>-1.872020484217921</v>
       </c>
       <c r="E20">
-        <v>0.0325044320211571</v>
+        <v>0.0612037696163709</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="B21">
-        <v>-0.01187383452271966</v>
+        <v>0.007950868810761291</v>
       </c>
       <c r="C21">
-        <v>0.008581307238178454</v>
+        <v>0.02073736540534542</v>
       </c>
       <c r="D21">
-        <v>-1.383685980836657</v>
+        <v>0.3834078560776006</v>
       </c>
       <c r="E21">
-        <v>0.1664546280563421</v>
+        <v>0.7014173792774256</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.006472588092971089</v>
+        <v>0.02612276664797638</v>
       </c>
       <c r="C22">
-        <v>0.01014089477437207</v>
+        <v>0.02355675285431198</v>
       </c>
       <c r="D22">
-        <v>-0.6382659752400277</v>
+        <v>1.108929011121951</v>
       </c>
       <c r="E22">
-        <v>0.5233005566236071</v>
+        <v>0.2674608074147826</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.01351820637137212</v>
+        <v>0.06103545304568189</v>
       </c>
       <c r="C23">
-        <v>0.01378867062994513</v>
+        <v>0.02905840750903886</v>
       </c>
       <c r="D23">
-        <v>-0.9803850374099414</v>
+        <v>2.100440398418128</v>
       </c>
       <c r="E23">
-        <v>0.3268960927402136</v>
+        <v>0.03569011842354605</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.01861712042437113</v>
+        <v>-0.001043605482404629</v>
       </c>
       <c r="C24">
-        <v>0.01348122884459471</v>
+        <v>0.02933160792997002</v>
       </c>
       <c r="D24">
-        <v>-1.380966129941162</v>
+        <v>-0.03557955243695687</v>
       </c>
       <c r="E24">
-        <v>0.1672893749907523</v>
+        <v>0.9716176127887691</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1065,16 +1065,16 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.01838248377624672</v>
+        <v>0.008420966898782429</v>
       </c>
       <c r="C25">
-        <v>0.01045410418002407</v>
+        <v>0.02495293420360454</v>
       </c>
       <c r="D25">
-        <v>1.758398755138902</v>
+        <v>0.3374740152829798</v>
       </c>
       <c r="E25">
-        <v>0.07867968480708418</v>
+        <v>0.735759597231054</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.01151155404756585</v>
+        <v>0.01859859971412807</v>
       </c>
       <c r="C26">
-        <v>0.01460811258822534</v>
+        <v>0.03448307159264383</v>
       </c>
       <c r="D26">
-        <v>0.7880247347521525</v>
+        <v>0.5393544964276226</v>
       </c>
       <c r="E26">
-        <v>0.4306822379300197</v>
+        <v>0.5896422724985635</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.0346930487612666</v>
+        <v>0.04639634401583818</v>
       </c>
       <c r="C27">
-        <v>0.009019008701857711</v>
+        <v>0.02577552480668989</v>
       </c>
       <c r="D27">
-        <v>3.846658752432584</v>
+        <v>1.80001549391523</v>
       </c>
       <c r="E27">
-        <v>0.0001197395574908256</v>
+        <v>0.0718581917658463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>***</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1152,16 +1152,16 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.008449242188402765</v>
+        <v>0.001262138201637078</v>
       </c>
       <c r="C28">
-        <v>0.01490636052079018</v>
+        <v>0.03623280753559788</v>
       </c>
       <c r="D28">
-        <v>0.5668212691232342</v>
+        <v>0.03483412651357632</v>
       </c>
       <c r="E28">
-        <v>0.5708356186636665</v>
+        <v>0.9722120081134195</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.02039879569662755</v>
+        <v>0.05716610025889696</v>
       </c>
       <c r="C29">
-        <v>0.01373953076225763</v>
+        <v>0.03315400386745411</v>
       </c>
       <c r="D29">
-        <v>1.484679211364544</v>
+        <v>1.724259322869131</v>
       </c>
       <c r="E29">
-        <v>0.1376288211758379</v>
+        <v>0.0846610390541446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1210,16 +1210,16 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.06082222147980457</v>
+        <v>-0.09991147588787019</v>
       </c>
       <c r="C30">
-        <v>0.0128979877759042</v>
+        <v>0.03061022819283887</v>
       </c>
       <c r="D30">
-        <v>-4.715636464893509</v>
+        <v>-3.263989907505624</v>
       </c>
       <c r="E30">
-        <v>2.409563281887003E-06</v>
+        <v>0.001098550785812458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>**</t>
         </is>
       </c>
     </row>
@@ -1239,16 +1239,16 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.01851097438474544</v>
+        <v>0.02331547717895013</v>
       </c>
       <c r="C31">
-        <v>0.01130707763010864</v>
+        <v>0.02720952872682036</v>
       </c>
       <c r="D31">
-        <v>-1.637113937862615</v>
+        <v>0.8568864758016969</v>
       </c>
       <c r="E31">
-        <v>0.1016066648406727</v>
+        <v>0.3915076277343874</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.01489620030501303</v>
+        <v>0.02347220054832351</v>
       </c>
       <c r="C32">
-        <v>0.01153278003111527</v>
+        <v>0.02671671223727239</v>
       </c>
       <c r="D32">
-        <v>-1.291640026500402</v>
+        <v>0.878558721592155</v>
       </c>
       <c r="E32">
-        <v>0.1964818357055724</v>
+        <v>0.3796405854221782</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1297,16 +1297,16 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.007563095479748976</v>
+        <v>-0.0019907462590275</v>
       </c>
       <c r="C33">
-        <v>0.0152994743733819</v>
+        <v>0.03735900910170136</v>
       </c>
       <c r="D33">
-        <v>-0.4943369487848082</v>
+        <v>-0.05328691276602516</v>
       </c>
       <c r="E33">
-        <v>0.6210682347723342</v>
+        <v>0.9575033074870367</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1326,16 +1326,16 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.02768945814607639</v>
+        <v>0.00167697979750836</v>
       </c>
       <c r="C34">
-        <v>0.01367310212005838</v>
+        <v>0.03148242146733282</v>
       </c>
       <c r="D34">
-        <v>-2.025104318167571</v>
+        <v>0.05326717956712601</v>
       </c>
       <c r="E34">
-        <v>0.04285665360525117</v>
+        <v>0.9575190299722376</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.0164078227780237</v>
+        <v>0.03099039773166076</v>
       </c>
       <c r="C35">
-        <v>0.0114307964356061</v>
+        <v>0.02829384393326567</v>
       </c>
       <c r="D35">
-        <v>1.435405036775436</v>
+        <v>1.09530531817293</v>
       </c>
       <c r="E35">
-        <v>0.1511717115565464</v>
+        <v>0.2733828983834354</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1384,16 +1384,16 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.03415763181440723</v>
+        <v>-0.03121252569291772</v>
       </c>
       <c r="C36">
-        <v>0.01525981995147892</v>
+        <v>0.0379701546820526</v>
       </c>
       <c r="D36">
-        <v>-2.238403331298598</v>
+        <v>-0.8220278783238928</v>
       </c>
       <c r="E36">
-        <v>0.02519476499514773</v>
+        <v>0.4110610304895165</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1413,16 +1413,16 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.003683375782054717</v>
+        <v>0.03623631528930488</v>
       </c>
       <c r="C37">
-        <v>0.01113987358445857</v>
+        <v>0.02801823228221075</v>
       </c>
       <c r="D37">
-        <v>0.3306478977637105</v>
+        <v>1.293311973586283</v>
       </c>
       <c r="E37">
-        <v>0.7409104620569897</v>
+        <v>0.1959031810984836</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1442,16 +1442,16 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.03873350276975595</v>
+        <v>-0.0834613258203635</v>
       </c>
       <c r="C38">
-        <v>0.01743553607801604</v>
+        <v>0.04183367209723581</v>
       </c>
       <c r="D38">
-        <v>-2.221526346906757</v>
+        <v>-1.995075297869399</v>
       </c>
       <c r="E38">
-        <v>0.02631533224075729</v>
+        <v>0.04603466805827713</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1471,16 +1471,16 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.01495858868782091</v>
+        <v>-0.0518726514508462</v>
       </c>
       <c r="C39">
-        <v>0.01889467604101384</v>
+        <v>0.04741796853050215</v>
       </c>
       <c r="D39">
-        <v>-0.7916827287936011</v>
+        <v>-1.093945039367904</v>
       </c>
       <c r="E39">
-        <v>0.4285456953623846</v>
+        <v>0.2739790836585555</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1500,16 +1500,16 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.01976585557889786</v>
+        <v>-0.03466763767798526</v>
       </c>
       <c r="C40">
-        <v>0.01772100643250281</v>
+        <v>0.04346281178554824</v>
       </c>
       <c r="D40">
-        <v>-1.115391253548925</v>
+        <v>-0.7976390908402421</v>
       </c>
       <c r="E40">
-        <v>0.2646827959756961</v>
+        <v>0.4250799593563103</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1529,16 +1529,16 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.02463111038503147</v>
+        <v>0.009997650603054586</v>
       </c>
       <c r="C41">
-        <v>0.01207012953560481</v>
+        <v>0.02840430308113192</v>
       </c>
       <c r="D41">
-        <v>-2.040666615248322</v>
+        <v>0.3519766203908629</v>
       </c>
       <c r="E41">
-        <v>0.04128397586600612</v>
+        <v>0.7248557961796396</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1558,16 +1558,16 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.003405795530291891</v>
+        <v>0.04443389108037731</v>
       </c>
       <c r="C42">
-        <v>0.01490272147422838</v>
+        <v>0.04115101553043655</v>
       </c>
       <c r="D42">
-        <v>-0.2285351394496375</v>
+        <v>1.079776294889069</v>
       </c>
       <c r="E42">
-        <v>0.8192302414785021</v>
+        <v>0.2802418096628149</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1587,16 +1587,16 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.01104589261941247</v>
+        <v>0.01793007754053122</v>
       </c>
       <c r="C43">
-        <v>0.01795786228666845</v>
+        <v>0.04272558847584919</v>
       </c>
       <c r="D43">
-        <v>-0.6151006418850151</v>
+        <v>0.4196566549496743</v>
       </c>
       <c r="E43">
-        <v>0.538488258202014</v>
+        <v>0.6747362940387691</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.009646757517610006</v>
+        <v>-0.05141154044563007</v>
       </c>
       <c r="C44">
-        <v>0.01727662320125976</v>
+        <v>0.03840514608599255</v>
       </c>
       <c r="D44">
-        <v>-0.5583705452872637</v>
+        <v>-1.338662801347378</v>
       </c>
       <c r="E44">
-        <v>0.5765913817855483</v>
+        <v>0.1806804713243028</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1645,16 +1645,16 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.005719426911005579</v>
+        <v>0.01806974187274473</v>
       </c>
       <c r="C45">
-        <v>0.01874279209648068</v>
+        <v>0.0465454071425213</v>
       </c>
       <c r="D45">
-        <v>0.3051534094581091</v>
+        <v>0.3882175059166518</v>
       </c>
       <c r="E45">
-        <v>0.7602493149117824</v>
+        <v>0.6978550792994377</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1674,16 +1674,16 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.06517740476827896</v>
+        <v>-0.08083318222183369</v>
       </c>
       <c r="C46">
-        <v>0.02485782267989147</v>
+        <v>0.06788551917849446</v>
       </c>
       <c r="D46">
-        <v>-2.62200779238013</v>
+        <v>-1.190727907807486</v>
       </c>
       <c r="E46">
-        <v>0.008741343231672182</v>
+        <v>0.2337604183351377</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.004926343265352978</v>
+        <v>-0.09808052154725365</v>
       </c>
       <c r="C47">
-        <v>0.01731356509074363</v>
+        <v>0.04622703513529001</v>
       </c>
       <c r="D47">
-        <v>-0.2845366185146208</v>
+        <v>-2.121713435875933</v>
       </c>
       <c r="E47">
-        <v>0.7759991756558706</v>
+        <v>0.0338618096505106</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -1732,16 +1732,16 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.06872441750547584</v>
+        <v>-0.04870502277551871</v>
       </c>
       <c r="C48">
-        <v>0.02460190473445825</v>
+        <v>0.06455444184388058</v>
       </c>
       <c r="D48">
-        <v>-2.793459215749996</v>
+        <v>-0.7544798062588421</v>
       </c>
       <c r="E48">
-        <v>0.00521476043508152</v>
+        <v>0.4505611665462678</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.02612718094776566</v>
+        <v>0.03908850793715064</v>
       </c>
       <c r="C49">
-        <v>0.01784395551630362</v>
+        <v>0.04795172219472111</v>
       </c>
       <c r="D49">
-        <v>1.464203434260629</v>
+        <v>0.8151637970044339</v>
       </c>
       <c r="E49">
-        <v>0.1431383721697725</v>
+        <v>0.4149785576813574</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.006111294785118076</v>
+        <v>0.06315703404322748</v>
       </c>
       <c r="C50">
-        <v>0.01730780304205899</v>
+        <v>0.04578740570476569</v>
       </c>
       <c r="D50">
-        <v>0.3530947729337609</v>
+        <v>1.379353843510158</v>
       </c>
       <c r="E50">
-        <v>0.7240173914288081</v>
+        <v>0.1677856829129034</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="B51">
-        <v>-0.02016425427442703</v>
+        <v>0.04687207045914749</v>
       </c>
       <c r="C51">
-        <v>0.01612791237259593</v>
+        <v>0.03732364447586351</v>
       </c>
       <c r="D51">
-        <v>-1.250270574925093</v>
+        <v>1.25582780345737</v>
       </c>
       <c r="E51">
-        <v>0.2112007235226919</v>
+        <v>0.2091784087866492</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1848,16 +1848,16 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.007580934698476749</v>
+        <v>0.09028198738838594</v>
       </c>
       <c r="C52">
-        <v>0.02003707329484139</v>
+        <v>0.04729635180635605</v>
       </c>
       <c r="D52">
-        <v>0.3783454093781494</v>
+        <v>1.908857320708891</v>
       </c>
       <c r="E52">
-        <v>0.7051740162448585</v>
+        <v>0.05628050000460433</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         </is>
       </c>
       <c r="B53">
-        <v>-0.03122412491772363</v>
+        <v>-0.02811616405034375</v>
       </c>
       <c r="C53">
-        <v>0.02468650594045579</v>
+        <v>0.05744821748518719</v>
       </c>
       <c r="D53">
-        <v>-1.264825609303992</v>
+        <v>-0.4894175186130605</v>
       </c>
       <c r="E53">
-        <v>0.2059338490009726</v>
+        <v>0.6245461358787404</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1906,16 +1906,16 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.04434783606459209</v>
+        <v>0.08588185380877524</v>
       </c>
       <c r="C54">
-        <v>0.01481116203187692</v>
+        <v>0.04388491019127877</v>
       </c>
       <c r="D54">
-        <v>2.99421719708053</v>
+        <v>1.956979140083611</v>
       </c>
       <c r="E54">
-        <v>0.002751499981810517</v>
+        <v>0.05034992091992203</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -1935,16 +1935,16 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.001639198858233569</v>
+        <v>-0.05468751106752658</v>
       </c>
       <c r="C55">
-        <v>0.01674579503105565</v>
+        <v>0.04617673385909195</v>
       </c>
       <c r="D55">
-        <v>0.09788719228878763</v>
+        <v>-1.184308774076686</v>
       </c>
       <c r="E55">
-        <v>0.9220218702147521</v>
+        <v>0.236290856871583</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1964,16 +1964,16 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.001542221380103572</v>
+        <v>-0.02024264903383842</v>
       </c>
       <c r="C56">
-        <v>0.01929891021276475</v>
+        <v>0.05039926575144194</v>
       </c>
       <c r="D56">
-        <v>0.07991235583258538</v>
+        <v>-0.401645713127463</v>
       </c>
       <c r="E56">
-        <v>0.9363069627262258</v>
+        <v>0.6879447821949736</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -1993,16 +1993,16 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.01321470254428619</v>
+        <v>-0.02311531009958613</v>
       </c>
       <c r="C57">
-        <v>0.01425651098382922</v>
+        <v>0.0397260940094076</v>
       </c>
       <c r="D57">
-        <v>0.9269240250489948</v>
+        <v>-0.5818671751144766</v>
       </c>
       <c r="E57">
-        <v>0.3539659822712366</v>
+        <v>0.5606561520861491</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2022,16 +2022,16 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.01242990750988507</v>
+        <v>0.1523370190552552</v>
       </c>
       <c r="C58">
-        <v>0.0219801348283024</v>
+        <v>0.06222068222917882</v>
       </c>
       <c r="D58">
-        <v>0.5655064269159933</v>
+        <v>2.448334116526542</v>
       </c>
       <c r="E58">
-        <v>0.5717293540920132</v>
+        <v>0.01435184994260604</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -2051,16 +2051,16 @@
         </is>
       </c>
       <c r="B59">
-        <v>-0.01516149119863781</v>
+        <v>-0.01060039059431308</v>
       </c>
       <c r="C59">
-        <v>0.02193158530501762</v>
+        <v>0.05648389879917019</v>
       </c>
       <c r="D59">
-        <v>-0.6913084935619809</v>
+        <v>-0.187671014566523</v>
       </c>
       <c r="E59">
-        <v>0.4893716953392392</v>
+        <v>0.8511345535312747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         </is>
       </c>
       <c r="B60">
-        <v>0.02692715267819313</v>
+        <v>0.04833596504479053</v>
       </c>
       <c r="C60">
-        <v>0.01678847469867301</v>
+        <v>0.04613355522390625</v>
       </c>
       <c r="D60">
-        <v>1.603907035123417</v>
+        <v>1.047739867655875</v>
       </c>
       <c r="E60">
-        <v>0.1087345458804685</v>
+        <v>0.2947584739621865</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2109,16 +2109,16 @@
         </is>
       </c>
       <c r="B61">
-        <v>-0.01738909065479892</v>
+        <v>0.005207414983186833</v>
       </c>
       <c r="C61">
-        <v>0.01751832237555035</v>
+        <v>0.04283961633142896</v>
       </c>
       <c r="D61">
-        <v>-0.9926230538529307</v>
+        <v>0.1215560602340514</v>
       </c>
       <c r="E61">
-        <v>0.3208936856369837</v>
+        <v>0.9032506141995033</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2138,16 +2138,16 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.03725202060046567</v>
+        <v>0.009155916098225291</v>
       </c>
       <c r="C62">
-        <v>0.01626144430002977</v>
+        <v>0.04388316653085911</v>
       </c>
       <c r="D62">
-        <v>2.290818694400809</v>
+        <v>0.208643013301849</v>
       </c>
       <c r="E62">
-        <v>0.02197390195607278</v>
+        <v>0.8347269297034372</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2167,16 +2167,16 @@
         </is>
       </c>
       <c r="B63">
-        <v>-0.01471321246113828</v>
+        <v>0.0133435778746938</v>
       </c>
       <c r="C63">
-        <v>0.0175553568209564</v>
+        <v>0.04501722468685764</v>
       </c>
       <c r="D63">
-        <v>-0.838103868306148</v>
+        <v>0.2964104954828397</v>
       </c>
       <c r="E63">
-        <v>0.4019723705590987</v>
+        <v>0.7669166110420925</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2196,16 +2196,16 @@
         </is>
       </c>
       <c r="B64">
-        <v>-0.01135662008378118</v>
+        <v>-0.03927943290006835</v>
       </c>
       <c r="C64">
-        <v>0.02827282753104204</v>
+        <v>0.07492439809273017</v>
       </c>
       <c r="D64">
-        <v>-0.4016796718089913</v>
+        <v>-0.5242542336003042</v>
       </c>
       <c r="E64">
-        <v>0.687919786922036</v>
+        <v>0.6001017242319048</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2225,16 +2225,16 @@
         </is>
       </c>
       <c r="B65">
-        <v>-0.005040343586612712</v>
+        <v>0.0272774784357135</v>
       </c>
       <c r="C65">
-        <v>0.02614998731436411</v>
+        <v>0.07487926951633539</v>
       </c>
       <c r="D65">
-        <v>-0.1927474581926112</v>
+        <v>0.3642861183329619</v>
       </c>
       <c r="E65">
-        <v>0.8471567540252658</v>
+        <v>0.7156443647486372</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2254,16 +2254,16 @@
         </is>
       </c>
       <c r="B66">
-        <v>0.02200645697938469</v>
+        <v>0.09850945408065989</v>
       </c>
       <c r="C66">
-        <v>0.02078999214069062</v>
+        <v>0.06014374299818579</v>
       </c>
       <c r="D66">
-        <v>1.058512039372693</v>
+        <v>1.637900289704806</v>
       </c>
       <c r="E66">
-        <v>0.2898220649138185</v>
+        <v>0.1014424955352468</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="B67">
-        <v>0.03520633393132249</v>
+        <v>0.04700853769476554</v>
       </c>
       <c r="C67">
-        <v>0.01816924792501195</v>
+        <v>0.05055449484184408</v>
       </c>
       <c r="D67">
-        <v>1.937688014199924</v>
+        <v>0.9298587166547347</v>
       </c>
       <c r="E67">
-        <v>0.05266129711349594</v>
+        <v>0.3524442403156001</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="B68">
-        <v>-0.053794376843204</v>
+        <v>-0.09971243987932131</v>
       </c>
       <c r="C68">
-        <v>0.03123901818002648</v>
+        <v>0.07324877878896931</v>
       </c>
       <c r="D68">
-        <v>-1.72202521004962</v>
+        <v>-1.361284672971739</v>
       </c>
       <c r="E68">
-        <v>0.08506495180893082</v>
+        <v>0.173423744715013</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2341,16 +2341,16 @@
         </is>
       </c>
       <c r="B69">
-        <v>-0.0133359730370928</v>
+        <v>-0.1126168196692887</v>
       </c>
       <c r="C69">
-        <v>0.02462177306906094</v>
+        <v>0.06839580305001366</v>
       </c>
       <c r="D69">
-        <v>-0.5416333340286703</v>
+        <v>-1.646545762273439</v>
       </c>
       <c r="E69">
-        <v>0.5880711235802255</v>
+        <v>0.09965144653842803</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
         </is>
       </c>
       <c r="B70">
-        <v>-0.03289269977608875</v>
+        <v>-0.3466110666074054</v>
       </c>
       <c r="C70">
-        <v>0.04109028454945858</v>
+        <v>0.1653196962944084</v>
       </c>
       <c r="D70">
-        <v>-0.8004982232843203</v>
+        <v>-2.096610835711587</v>
       </c>
       <c r="E70">
-        <v>0.4234221925446589</v>
+        <v>0.03602803928973818</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -2399,16 +2399,16 @@
         </is>
       </c>
       <c r="B71">
-        <v>-0.006112116703381947</v>
+        <v>0.001138934626869513</v>
       </c>
       <c r="C71">
-        <v>0.02188129039610121</v>
+        <v>0.05956606487531499</v>
       </c>
       <c r="D71">
-        <v>-0.2793307246848202</v>
+        <v>0.0191205282614112</v>
       </c>
       <c r="E71">
-        <v>0.7799910294092394</v>
+        <v>0.9847449552384889</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="B72">
-        <v>0.002381040046268487</v>
+        <v>0.01910931183419166</v>
       </c>
       <c r="C72">
-        <v>0.02635544148260659</v>
+        <v>0.06868525090237702</v>
       </c>
       <c r="D72">
-        <v>0.09034339446902707</v>
+        <v>0.2782156515865669</v>
       </c>
       <c r="E72">
-        <v>0.9280143373186616</v>
+        <v>0.7808468207580832</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2457,16 +2457,16 @@
         </is>
       </c>
       <c r="B73">
-        <v>-0.03072487188857212</v>
+        <v>0.01615749296890108</v>
       </c>
       <c r="C73">
-        <v>0.03518191645595382</v>
+        <v>0.08305129935516715</v>
       </c>
       <c r="D73">
-        <v>-0.8733143325787347</v>
+        <v>0.1945483465563121</v>
       </c>
       <c r="E73">
-        <v>0.3824917705056879</v>
+        <v>0.8457465437272673</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2486,16 +2486,16 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.0428984697431363</v>
+        <v>0.01232609605773012</v>
       </c>
       <c r="C74">
-        <v>0.02764738962179463</v>
+        <v>0.0747777783479576</v>
       </c>
       <c r="D74">
-        <v>1.551628212643958</v>
+        <v>0.1648363501837946</v>
       </c>
       <c r="E74">
-        <v>0.1207512085544296</v>
+        <v>0.8690727920653363</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2515,16 +2515,16 @@
         </is>
       </c>
       <c r="B75">
-        <v>0.02287847406590389</v>
+        <v>0.03334511371370298</v>
       </c>
       <c r="C75">
-        <v>0.02542660472023226</v>
+        <v>0.07623120104683918</v>
       </c>
       <c r="D75">
-        <v>0.8997848638319847</v>
+        <v>0.4374208100593161</v>
       </c>
       <c r="E75">
-        <v>0.3682347508992462</v>
+        <v>0.6618061949017122</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2544,16 +2544,16 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.008490649281633971</v>
+        <v>-0.01761004906174436</v>
       </c>
       <c r="C76">
-        <v>0.02487233841409021</v>
+        <v>0.07258271959104057</v>
       </c>
       <c r="D76">
-        <v>0.3413691604012596</v>
+        <v>-0.2426204082867969</v>
       </c>
       <c r="E76">
-        <v>0.7328256886608278</v>
+        <v>0.8082994699938469</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2573,16 +2573,16 @@
         </is>
       </c>
       <c r="B77">
-        <v>-0.0268527095434924</v>
+        <v>-0.01082390713240928</v>
       </c>
       <c r="C77">
-        <v>0.03420675972754205</v>
+        <v>0.0740861183044404</v>
       </c>
       <c r="D77">
-        <v>-0.7850117858977319</v>
+        <v>-0.1460989910138205</v>
       </c>
       <c r="E77">
-        <v>0.432446658418302</v>
+        <v>0.8838432429254832</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2602,16 +2602,16 @@
         </is>
       </c>
       <c r="B78">
-        <v>-0.01654895098181839</v>
+        <v>-0.07668259149293739</v>
       </c>
       <c r="C78">
-        <v>0.02627077905052425</v>
+        <v>0.06124266100492742</v>
       </c>
       <c r="D78">
-        <v>-0.6299375800767563</v>
+        <v>-1.252110705750812</v>
       </c>
       <c r="E78">
-        <v>0.5287354242649631</v>
+        <v>0.2105295272063894</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
         </is>
       </c>
       <c r="B79">
-        <v>0.01012928721046699</v>
+        <v>0.006120465648860748</v>
       </c>
       <c r="C79">
-        <v>0.02945140730858157</v>
+        <v>0.07277320765239455</v>
       </c>
       <c r="D79">
-        <v>0.3439321966633329</v>
+        <v>0.08410328259949057</v>
       </c>
       <c r="E79">
-        <v>0.7308972778346581</v>
+        <v>0.9329743147563835</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2660,16 +2660,16 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.01870580741975258</v>
+        <v>-0.08958333174236058</v>
       </c>
       <c r="C80">
-        <v>0.02579523960774362</v>
+        <v>0.07147782302096573</v>
       </c>
       <c r="D80">
-        <v>0.7251650965140553</v>
+        <v>-1.253302464403318</v>
       </c>
       <c r="E80">
-        <v>0.4683507526966605</v>
+        <v>0.210095651916947</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2689,16 +2689,16 @@
         </is>
       </c>
       <c r="B81">
-        <v>0.04643164127335257</v>
+        <v>0.05970421367495871</v>
       </c>
       <c r="C81">
-        <v>0.0263509239403135</v>
+        <v>0.08298710408762459</v>
       </c>
       <c r="D81">
-        <v>1.762049838499901</v>
+        <v>0.7194396566955523</v>
       </c>
       <c r="E81">
-        <v>0.078060877306945</v>
+        <v>0.4718700699305466</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -2718,16 +2718,16 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.006411252192304921</v>
+        <v>0.0591291504000978</v>
       </c>
       <c r="C82">
-        <v>0.03234616734986337</v>
+        <v>0.09033868069582464</v>
       </c>
       <c r="D82">
-        <v>0.1982074761117565</v>
+        <v>0.6545274952507768</v>
       </c>
       <c r="E82">
-        <v>0.8428827384365515</v>
+        <v>0.5127720189452389</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2747,16 +2747,16 @@
         </is>
       </c>
       <c r="B83">
-        <v>0.005961482651921807</v>
+        <v>0.05503490972275302</v>
       </c>
       <c r="C83">
-        <v>0.02049815692105954</v>
+        <v>0.05772070807354805</v>
       </c>
       <c r="D83">
-        <v>0.2908301792634369</v>
+        <v>0.9534690678539014</v>
       </c>
       <c r="E83">
-        <v>0.7711812027921534</v>
+        <v>0.3403524613275524</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -2776,16 +2776,16 @@
         </is>
       </c>
       <c r="B84">
-        <v>-0.02807860411730743</v>
+        <v>0.1992577128817652</v>
       </c>
       <c r="C84">
-        <v>0.03870927211490294</v>
+        <v>0.09633291034224999</v>
       </c>
       <c r="D84">
-        <v>-0.7253715346018419</v>
+        <v>2.068428247146751</v>
       </c>
       <c r="E84">
-        <v>0.4682241312206358</v>
+        <v>0.03859977131426088</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -2805,16 +2805,16 @@
         </is>
       </c>
       <c r="B85">
-        <v>0.03575935139720798</v>
+        <v>0.1455091740843895</v>
       </c>
       <c r="C85">
-        <v>0.02945405048157959</v>
+        <v>0.08395686993233027</v>
       </c>
       <c r="D85">
-        <v>1.214072455656708</v>
+        <v>1.733141959695148</v>
       </c>
       <c r="E85">
-        <v>0.2247200571268456</v>
+        <v>0.08307044004036593</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -2834,16 +2834,16 @@
         </is>
       </c>
       <c r="B86">
-        <v>0.03206293127076798</v>
+        <v>0.03105221005979415</v>
       </c>
       <c r="C86">
-        <v>0.02565285796672443</v>
+        <v>0.07340618621202748</v>
       </c>
       <c r="D86">
-        <v>1.249877550187912</v>
+        <v>0.4230189805815889</v>
       </c>
       <c r="E86">
-        <v>0.2113442814494319</v>
+        <v>0.672281412840108</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -2863,16 +2863,16 @@
         </is>
       </c>
       <c r="B87">
-        <v>-0.04717462095163126</v>
+        <v>-0.01211203066462792</v>
       </c>
       <c r="C87">
-        <v>0.03714814950199456</v>
+        <v>0.08880091811008288</v>
       </c>
       <c r="D87">
-        <v>-1.269905004261339</v>
+        <v>-0.1363953315168784</v>
       </c>
       <c r="E87">
-        <v>0.2041184704023702</v>
+        <v>0.8915087640998987</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -2892,16 +2892,16 @@
         </is>
       </c>
       <c r="B88">
-        <v>-0.01716842137604305</v>
+        <v>0.02571214473878232</v>
       </c>
       <c r="C88">
-        <v>0.02826836892831558</v>
+        <v>0.0717868543506338</v>
       </c>
       <c r="D88">
-        <v>-0.6073368229903762</v>
+        <v>0.3581734423574908</v>
       </c>
       <c r="E88">
-        <v>0.5436274058752903</v>
+        <v>0.7202135205440697</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -2921,16 +2921,16 @@
         </is>
       </c>
       <c r="B89">
-        <v>-0.03757223864915468</v>
+        <v>-0.03459667878918488</v>
       </c>
       <c r="C89">
-        <v>0.04182585625768164</v>
+        <v>0.096665582729733</v>
       </c>
       <c r="D89">
-        <v>-0.8983017207747959</v>
+        <v>-0.3579006903202934</v>
       </c>
       <c r="E89">
-        <v>0.3690247154020383</v>
+        <v>0.7204176340963897</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -2950,16 +2950,16 @@
         </is>
       </c>
       <c r="B90">
-        <v>-0.05307926915131607</v>
+        <v>0.05040569588456804</v>
       </c>
       <c r="C90">
-        <v>0.02631416981078992</v>
+        <v>0.05818746658482565</v>
       </c>
       <c r="D90">
-        <v>-2.017136376825817</v>
+        <v>0.8662637994573392</v>
       </c>
       <c r="E90">
-        <v>0.04368128337029357</v>
+        <v>0.3863455134425163</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -2979,16 +2979,16 @@
         </is>
       </c>
       <c r="B91">
-        <v>-0.03221302281359465</v>
+        <v>0.03859432386454533</v>
       </c>
       <c r="C91">
-        <v>0.05859645254531656</v>
+        <v>0.1244455222458587</v>
       </c>
       <c r="D91">
-        <v>-0.5497435666209002</v>
+        <v>0.3101302736172147</v>
       </c>
       <c r="E91">
-        <v>0.5824952704817472</v>
+        <v>0.7564618914314272</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         </is>
       </c>
       <c r="B92">
-        <v>-0.01352438988658443</v>
+        <v>-0.1629239232066866</v>
       </c>
       <c r="C92">
-        <v>0.031268426126836</v>
+        <v>0.0923514088858693</v>
       </c>
       <c r="D92">
-        <v>-0.4325254437727258</v>
+        <v>-1.764173662017793</v>
       </c>
       <c r="E92">
-        <v>0.665359563765066</v>
+        <v>0.07770274560148213</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3037,16 +3037,16 @@
         </is>
       </c>
       <c r="B93">
-        <v>0.0035550710185448</v>
+        <v>-0.02171540073722777</v>
       </c>
       <c r="C93">
-        <v>0.03043871471166251</v>
+        <v>0.08033160149938594</v>
       </c>
       <c r="D93">
-        <v>0.1167943867611034</v>
+        <v>-0.27032201937856</v>
       </c>
       <c r="E93">
-        <v>0.9070229920246901</v>
+        <v>0.7869125267154011</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3066,16 +3066,16 @@
         </is>
       </c>
       <c r="B94">
-        <v>0.07912881590207843</v>
+        <v>0.05213573155174272</v>
       </c>
       <c r="C94">
-        <v>0.05354111637893777</v>
+        <v>0.1753349212803905</v>
       </c>
       <c r="D94">
-        <v>1.477907470999362</v>
+        <v>0.2973493880797925</v>
       </c>
       <c r="E94">
-        <v>0.1394325463578538</v>
+        <v>0.7661997795059906</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3095,16 +3095,16 @@
         </is>
       </c>
       <c r="B95">
-        <v>0.04258385401187061</v>
+        <v>0.2423748947416301</v>
       </c>
       <c r="C95">
-        <v>0.03137862296027136</v>
+        <v>0.10218885632603</v>
       </c>
       <c r="D95">
-        <v>1.357097603224534</v>
+        <v>2.371832932236186</v>
       </c>
       <c r="E95">
-        <v>0.1747501999354673</v>
+        <v>0.01770009209682163</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -3124,16 +3124,16 @@
         </is>
       </c>
       <c r="B96">
-        <v>-0.08145724227900997</v>
+        <v>-0.2499415149288737</v>
       </c>
       <c r="C96">
-        <v>0.0542561535212629</v>
+        <v>0.1304468671569541</v>
       </c>
       <c r="D96">
-        <v>-1.501345690624512</v>
+        <v>-1.91604076338716</v>
       </c>
       <c r="E96">
-        <v>0.1332661729896425</v>
+        <v>0.05535990728720262</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3153,16 +3153,16 @@
         </is>
       </c>
       <c r="B97">
-        <v>0.0204047569332843</v>
+        <v>-0.02805263450066155</v>
       </c>
       <c r="C97">
-        <v>0.02846018096971155</v>
+        <v>0.08855577845933503</v>
       </c>
       <c r="D97">
-        <v>0.7169580880388585</v>
+        <v>-0.3167792660028772</v>
       </c>
       <c r="E97">
-        <v>0.4733999580314429</v>
+        <v>0.7514110979187095</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3182,16 +3182,16 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.05918264525536058</v>
+        <v>0.1143467620031016</v>
       </c>
       <c r="C98">
-        <v>0.03825588041385347</v>
+        <v>0.1341948605845031</v>
       </c>
       <c r="D98">
-        <v>1.54702086620725</v>
+        <v>0.8520949424221576</v>
       </c>
       <c r="E98">
-        <v>0.1218582141437474</v>
+        <v>0.3941613988328083</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3211,16 +3211,16 @@
         </is>
       </c>
       <c r="B99">
-        <v>-0.02996244954050826</v>
+        <v>0.1095997100662882</v>
       </c>
       <c r="C99">
-        <v>0.04258651272696497</v>
+        <v>0.1131703007830765</v>
       </c>
       <c r="D99">
-        <v>-0.7035666369915423</v>
+        <v>0.9684494015472102</v>
       </c>
       <c r="E99">
-        <v>0.4817026944937913</v>
+        <v>0.3328199773881157</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3240,16 +3240,16 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.04796040423913991</v>
+        <v>-0.1061097293960335</v>
       </c>
       <c r="C100">
-        <v>0.04497957800059426</v>
+        <v>0.1397868602855034</v>
       </c>
       <c r="D100">
-        <v>1.066270658175278</v>
+        <v>-0.7590822855546866</v>
       </c>
       <c r="E100">
-        <v>0.286301309368579</v>
+        <v>0.4478033351906279</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3269,16 +3269,16 @@
         </is>
       </c>
       <c r="B101">
-        <v>-0.04286355145130385</v>
+        <v>-0.07411219448420607</v>
       </c>
       <c r="C101">
-        <v>0.04814595654200803</v>
+        <v>0.1208078008488535</v>
       </c>
       <c r="D101">
-        <v>-0.8902835155825555</v>
+        <v>-0.613471927834612</v>
       </c>
       <c r="E101">
-        <v>0.3733136702274715</v>
+        <v>0.5395643389849182</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3298,16 +3298,16 @@
         </is>
       </c>
       <c r="B102">
-        <v>0.03467794734113636</v>
+        <v>0.1527906422293685</v>
       </c>
       <c r="C102">
-        <v>0.06853510374555385</v>
+        <v>0.1814879447129475</v>
       </c>
       <c r="D102">
-        <v>0.5059881060351654</v>
+        <v>0.8418776380493568</v>
       </c>
       <c r="E102">
-        <v>0.6128649993588547</v>
+        <v>0.3998564485117572</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3327,16 +3327,16 @@
         </is>
       </c>
       <c r="B103">
-        <v>0.001613121896286533</v>
+        <v>-0.05544232099538679</v>
       </c>
       <c r="C103">
-        <v>0.07623397235260483</v>
+        <v>0.2034413062419288</v>
       </c>
       <c r="D103">
-        <v>0.02116014483444945</v>
+        <v>-0.2725224391228385</v>
       </c>
       <c r="E103">
-        <v>0.9831179069726989</v>
+        <v>0.7852203400418981</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3356,16 +3356,16 @@
         </is>
       </c>
       <c r="B104">
-        <v>-0.03009068304027159</v>
+        <v>-0.2431145250842237</v>
       </c>
       <c r="C104">
-        <v>0.05555224393405486</v>
+        <v>0.1744390224093005</v>
       </c>
       <c r="D104">
-        <v>-0.5416645829103094</v>
+        <v>-1.393693462198981</v>
       </c>
       <c r="E104">
-        <v>0.5880495924363743</v>
+        <v>0.1634101913331394</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3385,16 +3385,16 @@
         </is>
       </c>
       <c r="B105">
-        <v>-0.01976404335429352</v>
+        <v>-0.01482693010670843</v>
       </c>
       <c r="C105">
-        <v>0.03681149674366985</v>
+        <v>0.08826322313557738</v>
       </c>
       <c r="D105">
-        <v>-0.5368986621738538</v>
+        <v>-0.1679853689903598</v>
       </c>
       <c r="E105">
-        <v>0.5913376151640194</v>
+        <v>0.8665947893651789</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         </is>
       </c>
       <c r="B106">
-        <v>-0.02963882318458224</v>
+        <v>-0.07198386066618914</v>
       </c>
       <c r="C106">
-        <v>0.0772806198845872</v>
+        <v>0.1811844401532959</v>
       </c>
       <c r="D106">
-        <v>-0.3835220683897928</v>
+        <v>-0.3972960404617818</v>
       </c>
       <c r="E106">
-        <v>0.7013327106563028</v>
+        <v>0.6911491668836574</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3443,16 +3443,16 @@
         </is>
       </c>
       <c r="B107">
-        <v>0.02045335838234351</v>
+        <v>0.2855954039151104</v>
       </c>
       <c r="C107">
-        <v>0.06435171445159397</v>
+        <v>0.1818428700451172</v>
       </c>
       <c r="D107">
-        <v>0.3178370391006247</v>
+        <v>1.570561462455202</v>
       </c>
       <c r="E107">
-        <v>0.7506085532626532</v>
+        <v>0.1162845473739926</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3472,16 +3472,16 @@
         </is>
       </c>
       <c r="B108">
-        <v>-0.2487945460937678</v>
+        <v>-0.1809553600693732</v>
       </c>
       <c r="C108">
-        <v>0.2986450037349527</v>
+        <v>0.3809484631119274</v>
       </c>
       <c r="D108">
-        <v>-0.8330778783581217</v>
+        <v>-0.4750127053700865</v>
       </c>
       <c r="E108">
-        <v>0.4048008088397569</v>
+        <v>0.6347779173698729</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3501,16 +3501,16 @@
         </is>
       </c>
       <c r="B109">
-        <v>-0.005329292883944292</v>
+        <v>0.1730459701622066</v>
       </c>
       <c r="C109">
-        <v>0.04985154456759455</v>
+        <v>0.1382855848641468</v>
       </c>
       <c r="D109">
-        <v>-0.106903265087769</v>
+        <v>1.251366657863933</v>
       </c>
       <c r="E109">
-        <v>0.9148657228722145</v>
+        <v>0.2108007360578089</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3530,16 +3530,16 @@
         </is>
       </c>
       <c r="B110">
-        <v>-0.05739590309520964</v>
+        <v>-0.2871419197313733</v>
       </c>
       <c r="C110">
-        <v>0.1038029826159342</v>
+        <v>0.3279939501470774</v>
       </c>
       <c r="D110">
-        <v>-0.5529311552402265</v>
+        <v>-0.87544882947571</v>
       </c>
       <c r="E110">
-        <v>0.5803105527795019</v>
+        <v>0.3813297410566622</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -3559,16 +3559,16 @@
         </is>
       </c>
       <c r="B111">
-        <v>0.1975783391763166</v>
+        <v>-0.007843959594657444</v>
       </c>
       <c r="C111">
-        <v>0.1272107305521095</v>
+        <v>4651.26003603445</v>
       </c>
       <c r="D111">
-        <v>1.553157806097045</v>
+        <v>-1.686416053690478E-06</v>
       </c>
       <c r="E111">
-        <v>0.1203854388109779</v>
+        <v>0.9999986544346676</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -3588,16 +3588,16 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.04719706284783509</v>
+        <v>0.05328203274619683</v>
       </c>
       <c r="C112">
-        <v>923.43211191486</v>
+        <v>4651.259957019603</v>
       </c>
       <c r="D112">
-        <v>5.111048472200698E-05</v>
+        <v>1.145539772847666E-05</v>
       </c>
       <c r="E112">
-        <v>0.9999592197333629</v>
+        <v>0.9999908599150148</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -3617,16 +3617,16 @@
         </is>
       </c>
       <c r="B113">
-        <v>0.0226267122492961</v>
+        <v>0.01684572214165758</v>
       </c>
       <c r="C113">
-        <v>83126.49089812193</v>
+        <v>154032.2213957847</v>
       </c>
       <c r="D113">
-        <v>2.721961676095159E-07</v>
+        <v>1.093649237088688E-07</v>
       </c>
       <c r="E113">
-        <v>0.9999997828188804</v>
+        <v>0.9999999127394159</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -3646,16 +3646,16 @@
         </is>
       </c>
       <c r="B114">
-        <v>-0.03143608820381232</v>
+        <v>-0.06114593850907203</v>
       </c>
       <c r="C114">
-        <v>1023.785691558143</v>
+        <v>3019.84107573403</v>
       </c>
       <c r="D114">
-        <v>-3.070573115352727E-05</v>
+        <v>-2.024806503905486E-05</v>
       </c>
       <c r="E114">
-        <v>0.9999755003711883</v>
+        <v>0.9999838443815203</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
